--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,13 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R5697e4c162fa410a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="Rcdd652f826014c95"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R1ea966fae57e4c5d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="Ra35561e77f654be2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="Rc9b8aaca119640cd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rf1541473b98a4baa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="7" r:id="R8ad4982abf744c5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rb0ff7fc8f78f4512"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R24806a1170ea4227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="Rd2db2859eb1143e3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R0b53755e09a54b28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R08c34fcb527b40d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R127dde07212e4472"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R8e0c3b3c278c492e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="Rce18cac80b4c4040"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -311,7 +312,19 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Mage_Guide" displayName="Mage_Guide" ref="A1:B20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Mage_Targeting" displayName="Mage_Targeting" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="4">
+    <x:tableColumn id="1" name="SkillId"/>
+    <x:tableColumn id="2" name="지점 선택"/>
+    <x:tableColumn id="3" name="판정과 대상"/>
+    <x:tableColumn id="4" name="표시 순서"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Mage_Guide" displayName="Mage_Guide" ref="A1:B22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Description"/>
@@ -653,10 +666,10 @@
         <x:v>ArcaneVolley</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>비전 탄막</x:v>
+        <x:v>유성우</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>추적 투사체</x:v>
+        <x:v>전장 낙하</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
         <x:v>62</x:v>
@@ -671,7 +684,7 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>추적 탄환을 연속 발사합니다. 적을 쓰러뜨리면 다음 적을 노립니다.</x:v>
+        <x:v>전장 곳곳의 적에게 별빛을 차례로 떨어뜨립니다. 별빛이 닿은 적에게 피해를 줍니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -845,13 +858,13 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="I11" s="5" t="str">
-        <x:v>적을 끌어모아 이동 속도를 20% 낮추고 지속 피해를 줍니다. 마지막에 균열이 폭발합니다. 보스는 끌어당기지 못합니다.</x:v>
+        <x:v>적이 모인 곳의 허공에 원형 균열을 엽니다. 균열 안의 적을 중심으로 끌어당기며 지속 피해를 주고, 닫힐 때 폭발합니다. 보스는 끌어당기지 못합니다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2b338307a1bc41bb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bbf21c663404b44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1028,7 +1041,7 @@
         <x:v>FireTornado</x:v>
       </x:c>
       <x:c r="C4" s="18" t="n">
-        <x:v>0.800000011920929</x:v>
+        <x:v>0.8500000238418579</x:v>
       </x:c>
       <x:c r="D4" s="18" t="n">
         <x:v>5</x:v>
@@ -1076,7 +1089,7 @@
         <x:v>ArcaneVolley</x:v>
       </x:c>
       <x:c r="C5" s="18" t="n">
-        <x:v>0.10000000149011612</x:v>
+        <x:v>0.550000011920929</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
         <x:v>1.3199999332427979</x:v>
@@ -1122,7 +1135,7 @@
         <x:v>VenomMist</x:v>
       </x:c>
       <x:c r="C6" s="18" t="n">
-        <x:v>1.25</x:v>
+        <x:v>1.399999976158142</x:v>
       </x:c>
       <x:c r="D6" s="18" t="n">
         <x:v>4.5</x:v>
@@ -1260,7 +1273,7 @@
         <x:v>Sanctuary</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:v>1.7000000476837158</x:v>
+        <x:v>1.899999976158142</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
         <x:v>4.199999809265137</x:v>
@@ -1306,7 +1319,7 @@
         <x:v>Meteor</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>1.350000023841858</x:v>
+        <x:v>1.5499999523162842</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
         <x:v>0.800000011920929</x:v>
@@ -1352,7 +1365,7 @@
         <x:v>VoidRift</x:v>
       </x:c>
       <x:c r="C11" s="18" t="n">
-        <x:v>1.600000023841858</x:v>
+        <x:v>1.2999999523162842</x:v>
       </x:c>
       <x:c r="D11" s="18" t="n">
         <x:v>3</x:v>
@@ -1392,7 +1405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7f957c6c4a94948"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8318e813f2de42f1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1582,7 +1595,7 @@
       </x:c>
       <x:c r="B5" s="16" t="str">
         <x:f>'Skills'!C5</x:f>
-        <x:v>비전 탄막</x:v>
+        <x:v>유성우</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>미정</x:v>
@@ -1810,7 +1823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24e44b919d1e4856"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc042dbc38d4e4c13"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1983,7 +1996,7 @@
       </x:c>
       <x:c r="B5" s="16" t="str">
         <x:f>'Skills'!C5</x:f>
-        <x:v>비전 탄막</x:v>
+        <x:v>유성우</x:v>
       </x:c>
       <x:c r="C5" s="9" t="n">
         <x:v>30</x:v>
@@ -2239,7 +2252,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5f86bd596c1b4de2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f054e3116543f5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4495,7 +4508,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd578b68dc8874a0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa243002569d4cdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4824,12 +4837,187 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc4d8085174344f21"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa305743c1c49b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetPr>
+    <x:tabColor rgb="FF2D6176"/>
+  </x:sheetPr>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="9" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="42" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="56" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="46" customHeight="1">
+      <x:c r="A1" s="8" t="str">
+        <x:v>SkillId</x:v>
+      </x:c>
+      <x:c r="B1" s="8" t="str">
+        <x:v>지점 선택</x:v>
+      </x:c>
+      <x:c r="C1" s="8" t="str">
+        <x:v>판정과 대상</x:v>
+      </x:c>
+      <x:c r="D1" s="8" t="str">
+        <x:v>표시 순서</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="68" customHeight="1">
+      <x:c r="A2" s="9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B2" s="5" t="str">
+        <x:v>적이 가장 많이 모인 지점</x:v>
+      </x:c>
+      <x:c r="C2" s="5" t="str">
+        <x:v>지정 지점 고정 원형 범위 · 천벌은 가장자리/HUD 안쪽 보정</x:v>
+      </x:c>
+      <x:c r="D2" s="5" t="str">
+        <x:v>즉발 낙뢰 전면 · 구름 전면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="68" customHeight="1">
+      <x:c r="A3" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B3" s="5" t="str">
+        <x:v>전장의 유효 적 순회</x:v>
+      </x:c>
+      <x:c r="C3" s="5" t="str">
+        <x:v>개화는 시전 시작 시 단일/다수 분기</x:v>
+      </x:c>
+      <x:c r="D3" s="5" t="str">
+        <x:v>빙정 전면 · 바닥 예고 후면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="68" customHeight="1">
+      <x:c r="A4" s="9" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B4" s="5" t="str">
+        <x:v>현재 중심에 가까운 살아 있는 적 추적</x:v>
+      </x:c>
+      <x:c r="C4" s="5" t="str">
+        <x:v>이동 장판 안 최대 3체</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="str">
+        <x:v>지속 장판 후면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="68" customHeight="1">
+      <x:c r="A5" s="9" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B5" s="5" t="str">
+        <x:v>전장 내 적을 차례로 선택</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="str">
+        <x:v>별빛은 선택 순간 위치로 낙하 · 회피 가능</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="str">
+        <x:v>낙하와 충돌 전면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="68" customHeight="1">
+      <x:c r="A6" s="9" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B6" s="5" t="str">
+        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="str">
+        <x:v>고정 장판 안 최대 5체 · 틱마다 재판정</x:v>
+      </x:c>
+      <x:c r="D6" s="5" t="str">
+        <x:v>지속 장판 후면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="68" customHeight="1">
+      <x:c r="A7" s="9" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B7" s="5" t="str">
+        <x:v>적이 가장 많이 모인 지점</x:v>
+      </x:c>
+      <x:c r="C7" s="5" t="str">
+        <x:v>고정 범위 최대 4체</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>바닥 예고 후면 · 솟는 바위 전면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="68" customHeight="1">
+      <x:c r="A8" s="9" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>유효 표적 방향으로 관통 경로 설정</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>경로 안 최대 5체</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>단발 파동 전면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="68" customHeight="1">
+      <x:c r="A9" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B9" s="5" t="str">
+        <x:v>생존 아군 중 HP 비율 최저</x:v>
+      </x:c>
+      <x:c r="C9" s="5" t="str">
+        <x:v>매 회복마다 대상 재선정</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="str">
+        <x:v>성역 후면 · 회복 반짝임 전면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="68" customHeight="1">
+      <x:c r="A10" s="9" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B10" s="5" t="str">
+        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
+      </x:c>
+      <x:c r="C10" s="5" t="str">
+        <x:v>예고 위치 고정 · 충돌 후 잔불 2회</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="str">
+        <x:v>운석과 폭발 전면 · 잔불 후면</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="68" customHeight="1">
+      <x:c r="A11" s="9" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B11" s="5" t="str">
+        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
+      </x:c>
+      <x:c r="C11" s="5" t="str">
+        <x:v>허공 원 안 몸체 중심만 흡인 · 보스 흡인 면역</x:v>
+      </x:c>
+      <x:c r="D11" s="5" t="str">
+        <x:v>지속 균열 후면 · 붕괴 전면</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c52c43f33d4793"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr>
     <x:tabColor rgb="FF70858C"/>
@@ -4850,160 +5038,176 @@
     </x:row>
     <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="5" t="str">
-        <x:v>용도</x:v>
+        <x:v>편성 조작</x:v>
       </x:c>
       <x:c r="B2" s="5" t="str">
-        <x:v>개발자 열람용 스킬 카탈로그입니다. 현재 런타임 원본은 MageTowerSkillList와 각 MageTowerSkillSO입니다. 이 파일의 편집 내용은 자동으로 게임에 반영되지 않습니다.</x:v>
+        <x:v>슬롯 선택 → 스킬 선택 → 장착 또는 교체. 다른 슬롯의 스킬을 고르면 원자적으로 자리 바꾸기. 해제·교체는 진행 중인 효과를 취소하지 않으며 슬롯 및 스킬 쿨타임을 모두 보존합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="5" t="str">
-        <x:v>수정 절차</x:v>
+        <x:v>시전 기록</x:v>
       </x:c>
       <x:c r="B3" s="5" t="str">
-        <x:v>스킬 데이터와 동작을 수정한 뒤 카탈로그를 함께 갱신합니다. 향후 임포터 연결 시 SkillId와 Key를 고정 키로 사용하고 수치 검증 후 데이터베이스를 교체합니다.</x:v>
+        <x:v>스킬 시전 카운터는 메모리에 즉시 반영하고 짧게 묶어 비동기로 저장합니다. 재화 거래는 앞선 저장 완료를 확인한 뒤 기록하며 앱 백그라운드와 계정 전환에서 남은 카운터를 저장합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="5" t="str">
-        <x:v>버전</x:v>
+        <x:v>용도</x:v>
       </x:c>
       <x:c r="B4" s="5" t="str">
-        <x:v>게임 0.9.0 · 스킬 데이터 계약 mage-2 · 스킬 ID 0~9. 기존 0~2와 에셋 GUID를 유지했습니다.</x:v>
+        <x:v>개발자 열람용 스킬 카탈로그입니다. 현재 런타임 원본은 MageTowerSkillList와 각 MageTowerSkillSO입니다. 이 파일의 편집 내용은 자동으로 게임에 반영되지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="5" t="str">
-        <x:v>단위</x:v>
+        <x:v>수정 절차</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>BasePower는 강화 전 한 번의 피해 또는 회복량입니다. RadiusWU는 월드 단위입니다. Bloom 배율은 강화·각성을 반영한 1회 효과량에 곱합니다.</x:v>
+        <x:v>스킬 데이터와 동작을 수정한 뒤 카탈로그를 함께 갱신합니다. 향후 임포터 연결 시 SkillId와 Key를 고정 키로 사용하고 수치 검증 후 데이터베이스를 교체합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="5" t="str">
-        <x:v>공통 성장</x:v>
+        <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>직접 강화 E는 비전 지식으로 0~100, 각성 A는 동일 스킬 파편으로 0~10. A4/A8에 각각 1회 추가(화염 회오리는 2틱), A마다 효과량 +5%와 쿨타임 -2%. 운석은 고정 1회 충돌과 잔불 2회이며 타격 수 보너스를 사용하지 않습니다.</x:v>
+        <x:v>게임 0.10.0 · 스킬 데이터 계약 mage-3 · 스킬 ID 0~9. 기존 0~2와 에셋 GUID를 유지했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="5" t="str">
-        <x:v>개화 저장</x:v>
+        <x:v>단위</x:v>
       </x:c>
       <x:c r="B7" s="5" t="str">
-        <x:v>A10에서 해금되며 기본은 꺼짐입니다. 마탑 상세에서 전환하고 다음 시전부터 적용합니다. 진행 중인 시전의 배율·대상 조건·쿨타임은 바뀌지 않습니다.</x:v>
+        <x:v>BasePower는 강화 전 한 번의 피해 또는 회복량입니다. RadiusWU는 월드 단위입니다. Bloom 배율은 강화·각성을 반영한 1회 효과량에 곱합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="5" t="str">
-        <x:v>회복과 전투력</x:v>
+        <x:v>공통 성장</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>회복의 성역은 살아있는 아군 중 HP 비율이 가장 낮은 대상을 반복 회복합니다. 전원이 HP 90% 이상이면 자동 시전을 보류합니다. 회복·제어 효용은 단일 대상 DPS 기반 전투력에 더하지 않습니다.</x:v>
+        <x:v>직접 강화 E는 비전 지식으로 0~100, 각성 A는 동일 스킬 파편으로 0~10. A4/A8에 각각 1회 추가(화염 회오리는 2틱), A마다 효과량 +5%와 쿨타임 -2%. 운석은 고정 1회 충돌과 잔불 2회이며 타격 수 보너스를 사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="5" t="str">
-        <x:v>확률</x:v>
+        <x:v>개화 저장</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>전체 뽑기는 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 스킬 10종은 등급 없이 각각 5%로 획득합니다. 희귀도는 장비에만 적용합니다.</x:v>
+        <x:v>A10에서 해금되며 기본은 꺼짐입니다. 마탑 상세에서 전환하고 다음 시전부터 적용합니다. 진행 중인 시전의 배율·대상 조건·쿨타임은 바뀌지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="5" t="str">
-        <x:v>파편</x:v>
+        <x:v>회복과 전투력</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>첫 획득은 해금만 지급합니다. 모든 스킬의 중복 뽑기는 30파편입니다. 메인 최초 보상의 기존 중복 대체 및 명시적 파편 보상은 1개 단위를 유지합니다.</x:v>
+        <x:v>회복의 성역은 살아있는 아군 중 HP 비율이 가장 낮은 대상을 반복 회복합니다. 전원이 HP 90% 이상이면 자동 시전을 보류합니다. 회복·제어 효용은 단일 대상 DPS 기반 전투력에 더하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="5" t="str">
-        <x:v>투자 기간</x:v>
+        <x:v>확률</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>각성 누적55파편 기준입니다. 주당21회 전부 마탑에 사용하고 최초 보상·기존 파편을 제외하면 미보유 특정 스킬의 평균 개화 기간은 60회 뽑기, 약2.86주입니다. 장비 뽑기에 주화를 나누면 더 오래 걸립니다.</x:v>
+        <x:v>전체 뽑기는 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 스킬 10종은 등급 없이 각각 5%로 획득합니다. 희귀도는 장비에만 적용합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
       <x:c r="A12" s="5" t="str">
-        <x:v>확률 편차</x:v>
+        <x:v>파편</x:v>
       </x:c>
       <x:c r="B12" s="5" t="str">
-        <x:v>Acquisition의 P90은 해당 횟수까지 약90%가 목표를 달성한다는 정확한 음이항 계산입니다. 스킬당105회(약5주). 천장과 기간 보장은 없으며 수 주는 평균 목표입니다.</x:v>
+        <x:v>첫 획득은 해금만 지급합니다. 모든 스킬의 중복 뽑기는 30파편입니다. 메인 최초 보상의 기존 중복 대체 및 명시적 파편 보상은 1개 단위를 유지합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="62" customHeight="1">
       <x:c r="A13" s="5" t="str">
-        <x:v>특수 개화</x:v>
+        <x:v>투자 기간</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>천벌은 약2초 예고 후 큰 범위의 최대10체를 공격합니다. 실제 반경은 뷰포트 폭의1/4을 월드 단위1.6~2.6으로 제한합니다. 만년빙정은 시전 시작 시 화면 내 유효 적 1체 여부로 단일/다수 형태를 선택합니다.</x:v>
+        <x:v>각성 누적55파편 기준입니다. 주당21회 전부 마탑에 사용하고 최초 보상·기존 파편을 제외하면 미보유 특정 스킬의 평균 개화 기간은 60회 뽑기, 약2.86주입니다. 장비 뽑기에 주화를 나누면 더 오래 걸립니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
       <x:c r="A14" s="5" t="str">
-        <x:v>최적화</x:v>
+        <x:v>확률 편차</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>아이콘48px·16색 이내·Point. Atlas_UIPixel ASTC4×4. VFX는 공유 시트와 사전 생성 AnimationClip·프리팹을 사용하고 Atlas_MageVFX에 포함합니다. 저사양은 동시 얼음 연출만 줄이고 피해 수는 유지합니다.</x:v>
+        <x:v>Acquisition의 P90은 해당 횟수까지 약90%가 목표를 달성한다는 정확한 음이항 계산입니다. 스킬당105회(약5주). 천장과 기간 보장은 없으며 수 주는 평균 목표입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="62" customHeight="1">
       <x:c r="A15" s="5" t="str">
-        <x:v>개화 아이콘</x:v>
+        <x:v>특수 개화</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>개화 ON이면 BloomIcon을 사용합니다. 기본 실루엣과 구도를 유지하고 작은 발광·색조만 변화합니다. OFF 및 미해금 상태는 원본 아이콘을 사용합니다.</x:v>
+        <x:v>천벌은 약2초 예고 후 큰 범위의 최대10체를 공격합니다. 실제 반경은 뷰포트 폭의1/4을 월드 단위1.6~2.6으로 제한합니다. 만년빙정은 시전 시작 시 화면 내 유효 적 1체 여부로 단일/다수 형태를 선택합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="62" customHeight="1">
       <x:c r="A16" s="5" t="str">
-        <x:v>타격 연출</x:v>
+        <x:v>최적화</x:v>
       </x:c>
       <x:c r="B16" s="5" t="str">
-        <x:v>피해·피격 반응·효과음은 스프라이트의 적중 프레임에 맞춥니다. 일회 연출은 반복하지 않으며, 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
+        <x:v>아이콘48px·16색 이내·Point. Atlas_UIPixel ASTC4×4. VFX는 공유 시트와 사전 생성 AnimationClip·프리팹을 사용하고 Atlas_MageVFX에 포함합니다. 저사양은 동시 얼음 연출만 줄이고 피해 수는 유지합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="62" customHeight="1">
       <x:c r="A17" s="5" t="str">
-        <x:v>외부 원본</x:v>
+        <x:v>개화 아이콘</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>ExternalAssets는 원본 저장소이며 직접 변경하지 않습니다. Assets 탭의 작업본만 게임에서 사용합니다. 출처 및 생성 공정은 AI/comfyui/mage-skills/20260915 및20260916 기록을 따릅니다.</x:v>
+        <x:v>개화 ON이면 BloomIcon을 사용합니다. 기본 실루엣과 구도를 유지하고 작은 발광·색조만 변화합니다. OFF 및 미해금 상태는 원본 아이콘을 사용합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="62" customHeight="1">
       <x:c r="A18" s="5" t="str">
-        <x:v>서버 계약</x:v>
+        <x:v>타격 연출</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>MageSkillStateSnapshot schema1은 catalogVersion·progressionRevision·정렬된 스킬 상태·장착 ID를 내보냅니다. 기존 계정/권한/전체 저장 리비전 계약과 함께 사용해야 합니다. 서버 응답을 적용하는 기능은 추가하지 않았습니다.</x:v>
+        <x:v>피해·피격 반응·효과음은 스프라이트의 적중 프레임에 맞춥니다. 일회 연출은 반복하지 않으며, 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="62" customHeight="1">
       <x:c r="A19" s="5" t="str">
-        <x:v>레거시 코드</x:v>
+        <x:v>외부 원본</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>64비트 packed code는 개화를 담지 못하고 파편 상한65535입니다. 범위를 넘으면 예외로 거부하며 새 스냅샷을 사용합니다. 기존 저장 JSON의 BloomEnabled 누락은 false로 읽습니다.</x:v>
+        <x:v>ExternalAssets는 원본 저장소이며 직접 변경하지 않습니다. Assets 탭의 작업본만 게임에서 사용합니다. 출처 및 생성 공정은 AI/comfyui/mage-skills/20260915 및20260916-combat 기록을 따릅니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
       <x:c r="A20" s="5" t="str">
+        <x:v>서버 계약</x:v>
+      </x:c>
+      <x:c r="B20" s="5" t="str">
+        <x:v>MageSkillStateSnapshot schema1은 catalogVersion·progressionRevision·정렬된 스킬 상태·장착 ID를 내보냅니다. 기존 계정/권한/전체 저장 리비전 계약과 함께 사용해야 합니다. 서버 응답을 적용하는 기능은 추가하지 않았습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="62" customHeight="1">
+      <x:c r="A21" s="5" t="str">
+        <x:v>레거시 코드</x:v>
+      </x:c>
+      <x:c r="B21" s="5" t="str">
+        <x:v>64비트 packed code는 개화를 담지 못하고 파편 상한65535입니다. 범위를 넘으면 예외로 거부하며 새 스냅샷을 사용합니다. 기존 저장 JSON의 BloomEnabled 누락은 false로 읽습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="62" customHeight="1">
+      <x:c r="A22" s="5" t="str">
         <x:v>보류 개화</x:v>
       </x:c>
-      <x:c r="B20" s="5" t="str">
+      <x:c r="B22" s="5" t="str">
         <x:v>천벌·만년빙정 외 8종은 개화 미정으로 표기합니다. 현재는 기존 피해 또는 회복의15% 증가만 적용하며 확정된 고유 개화로 오해하지 않도록 유지합니다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R350e59f2384a4db4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0e0f27093e4d00"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rb0ff7fc8f78f4512"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R24806a1170ea4227"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="Rd2db2859eb1143e3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R0b53755e09a54b28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R08c34fcb527b40d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R127dde07212e4472"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R8e0c3b3c278c492e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="Rce18cac80b4c4040"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R5fec058bdb964bba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R9965d484d4754f36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R14d5c4838099422b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R6e313ad36a9e4994"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R132f15671c6848ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R0f0ccff8863e4ae8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Reff0faa5f516437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R70b674a9002e4db8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -864,7 +864,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bbf21c663404b44"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912139e06cfc4334"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1405,7 +1405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8318e813f2de42f1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fc8405df4b44b04"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1510,10 +1510,10 @@
       <x:c r="K2" s="5"/>
       <x:c r="L2" s="5"/>
       <x:c r="M2" s="9" t="n">
-        <x:v>1.6</x:v>
+        <x:v>2.1</x:v>
       </x:c>
       <x:c r="N2" s="9" t="n">
-        <x:v>2.6</x:v>
+        <x:v>2.1</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="90" customHeight="1">
@@ -1823,7 +1823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc042dbc38d4e4c13"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9efe7a4b140c4cc2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2252,7 +2252,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R57f054e3116543f5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77fad7a1690a4689"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4508,7 +4508,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfa243002569d4cdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c402cd58564257"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4837,7 +4837,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fa305743c1c49b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488c3cb391bc44fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4869,7 +4869,7 @@
         <x:v>표시 순서</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="68" customHeight="1">
+    <x:row r="2" ht="76" customHeight="1">
       <x:c r="A2" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -4877,13 +4877,14 @@
         <x:v>적이 가장 많이 모인 지점</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>지정 지점 고정 원형 범위 · 천벌은 가장자리/HUD 안쪽 보정</x:v>
+        <x:v>고정 원형 범위 · 천벌의 구름 높이와 벼락 길이는 상단 여백에 맞춤
+연출 높이 보정으로 타격 지점을 아래로 이동하지 않음</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>즉발 낙뢰 전면 · 구름 전면</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="68" customHeight="1">
+    <x:row r="3" ht="76" customHeight="1">
       <x:c r="A3" s="9" t="n">
         <x:v>1</x:v>
       </x:c>
@@ -4897,7 +4898,7 @@
         <x:v>빙정 전면 · 바닥 예고 후면</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="68" customHeight="1">
+    <x:row r="4" ht="76" customHeight="1">
       <x:c r="A4" s="9" t="n">
         <x:v>2</x:v>
       </x:c>
@@ -4911,7 +4912,7 @@
         <x:v>지속 장판 후면</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="68" customHeight="1">
+    <x:row r="5" ht="76" customHeight="1">
       <x:c r="A5" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -4919,13 +4920,14 @@
         <x:v>전장 내 적을 차례로 선택</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>별빛은 선택 순간 위치로 낙하 · 회피 가능</x:v>
+        <x:v>별빛은 비행 전반 70% 동안 대상을 추적한 뒤 낙하 지점을 확정
+0.22초 간격 · 비행 0.48초</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>낙하와 충돌 전면</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="68" customHeight="1">
+    <x:row r="6" ht="76" customHeight="1">
       <x:c r="A6" s="9" t="n">
         <x:v>4</x:v>
       </x:c>
@@ -4933,13 +4935,13 @@
         <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>고정 장판 안 최대 5체 · 틱마다 재판정</x:v>
+        <x:v>고정 장판 안 최대 5체 · 틱마다 재판정 · 감속 25%, 기절과 별도 유지</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>지속 장판 후면</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="68" customHeight="1">
+    <x:row r="7" ht="76" customHeight="1">
       <x:c r="A7" s="9" t="n">
         <x:v>5</x:v>
       </x:c>
@@ -4947,13 +4949,13 @@
         <x:v>적이 가장 많이 모인 지점</x:v>
       </x:c>
       <x:c r="C7" s="5" t="str">
-        <x:v>고정 범위 최대 4체</x:v>
+        <x:v>고정 범위 최대 4체 · 기절이 기존 감속을 지우지 않음</x:v>
       </x:c>
       <x:c r="D7" s="5" t="str">
         <x:v>바닥 예고 후면 · 솟는 바위 전면</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="68" customHeight="1">
+    <x:row r="8" ht="76" customHeight="1">
       <x:c r="A8" s="9" t="n">
         <x:v>6</x:v>
       </x:c>
@@ -4961,13 +4963,13 @@
         <x:v>유효 표적 방향으로 관통 경로 설정</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>경로 안 최대 5체</x:v>
+        <x:v>파동이 실제 통과한 경로 안 최대 5체 · 파동당 같은 적 1회</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
         <x:v>단발 파동 전면</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="68" customHeight="1">
+    <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" s="9" t="n">
         <x:v>7</x:v>
       </x:c>
@@ -4981,7 +4983,7 @@
         <x:v>성역 후면 · 회복 반짝임 전면</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="76" customHeight="1">
       <x:c r="A10" s="9" t="n">
         <x:v>8</x:v>
       </x:c>
@@ -4995,7 +4997,7 @@
         <x:v>운석과 폭발 전면 · 잔불 후면</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="68" customHeight="1">
+    <x:row r="11" ht="76" customHeight="1">
       <x:c r="A11" s="9" t="n">
         <x:v>9</x:v>
       </x:c>
@@ -5003,7 +5005,8 @@
         <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
       </x:c>
       <x:c r="C11" s="5" t="str">
-        <x:v>허공 원 안 몸체 중심만 흡인 · 보스 흡인 면역</x:v>
+        <x:v>허공 원 안 몸체 중심만 흡인 · 보스 흡인 면역
+약한 감속으로 기존 강한 감속을 덮어쓰지 않음</x:v>
       </x:c>
       <x:c r="D11" s="5" t="str">
         <x:v>지속 균열 후면 · 붕괴 전면</x:v>
@@ -5012,7 +5015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8c52c43f33d4793"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27e6369b610a4dcc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5073,7 +5076,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.10.0 · 스킬 데이터 계약 mage-3 · 스킬 ID 0~9. 기존 0~2와 에셋 GUID를 유지했습니다.</x:v>
+        <x:v>게임 0.10.2 · 스킬 데이터 계약 mage-3 · 스킬 ID 0~9와 기존 에셋 GUID를 유지합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -5140,12 +5143,12 @@
         <x:v>Acquisition의 P90은 해당 횟수까지 약90%가 목표를 달성한다는 정확한 음이항 계산입니다. 스킬당105회(약5주). 천장과 기간 보장은 없으며 수 주는 평균 목표입니다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="62" customHeight="1">
+    <x:row r="15" ht="84" customHeight="1">
       <x:c r="A15" s="5" t="str">
         <x:v>특수 개화</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>천벌은 약2초 예고 후 큰 범위의 최대10체를 공격합니다. 실제 반경은 뷰포트 폭의1/4을 월드 단위1.6~2.6으로 제한합니다. 만년빙정은 시전 시작 시 화면 내 유효 적 1체 여부로 단일/다수 형태를 선택합니다.</x:v>
+        <x:v>천벌은 약 2초 예고 후 고정 반경 2.1 월드 단위 안 최대 10체를 공격합니다. 기기 비율이 피해 범위를 바꾸지 않습니다. Bloom의 최소·최대 반경은 모두 2.1입니다. 만년빙정은 시전 시작 시 유효 적 1체 여부로 단일/다수 형태를 선택합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="62" customHeight="1">
@@ -5164,20 +5167,20 @@
         <x:v>개화 ON이면 BloomIcon을 사용합니다. 기본 실루엣과 구도를 유지하고 작은 발광·색조만 변화합니다. OFF 및 미해금 상태는 원본 아이콘을 사용합니다.</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="62" customHeight="1">
+    <x:row r="18" ht="84" customHeight="1">
       <x:c r="A18" s="5" t="str">
         <x:v>타격 연출</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>피해·피격 반응·효과음은 스프라이트의 적중 프레임에 맞춥니다. 일회 연출은 반복하지 않으며, 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="62" customHeight="1">
+        <x:v>타격 시점에 피해·피격 반응·효과음을 맞춥니다. 별빛은 겹쳐 낙하하고 운석은 충돌 후 잔불을 남깁니다. 기절과 감속은 독립 만료하며 감속은 합산하지 않고 가장 강한 효과만 적용합니다. 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="84" customHeight="1">
       <x:c r="A19" s="5" t="str">
         <x:v>외부 원본</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>ExternalAssets는 원본 저장소이며 직접 변경하지 않습니다. Assets 탭의 작업본만 게임에서 사용합니다. 출처 및 생성 공정은 AI/comfyui/mage-skills/20260915 및20260916-combat 기록을 따릅니다.</x:v>
+        <x:v>ExternalAssets는 원본 저장소이며 직접 변경하지 않습니다. Assets 탭의 작업본만 사용합니다. 생성 출처는 AI/comfyui/mage-skills/20260915, 20260916-combat 및 20260917-polish입니다. 운석 잔흔은 두 모델 비교 후 채택한 단일 64px·6색 지면 데칼입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
@@ -5207,7 +5210,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b0e0f27093e4d00"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6882e447a3e4987"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R5fec058bdb964bba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R9965d484d4754f36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R14d5c4838099422b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R6e313ad36a9e4994"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R132f15671c6848ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R0f0ccff8863e4ae8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Reff0faa5f516437b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R70b674a9002e4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Re32e84b2bce343ff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R7e85d5c0db3a4613"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R8a02e866d6fb41da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R4ea15bbc3c7c46b3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R91ce146a850c4c4d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R4c4b104688a949c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R2bfd5c4faade442e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R6f00d504520941a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -695,7 +695,7 @@
         <x:v>VenomMist</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
-        <x:v>맹독 안개</x:v>
+        <x:v>맹독 늪</x:v>
       </x:c>
       <x:c r="D6" s="5" t="str">
         <x:v>지속 둔화</x:v>
@@ -713,7 +713,7 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="I6" s="5" t="str">
-        <x:v>독 안개로 지속 피해를 주고 이동 속도를 25% 낮춥니다.</x:v>
+        <x:v>맹독 늪을 펼쳐 범위 안의 적에게 지속 피해를 주고 이동 속도를 25% 낮춥니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="70" customHeight="1">
@@ -800,7 +800,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I9" s="5" t="str">
-        <x:v>체력 비율이 가장 낮은 왕국군을 반복해서 회복합니다.</x:v>
+        <x:v>성역을 펼쳐 범위 안에서 체력 비율이 가장 낮은 왕국군을 반복해서 회복합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -864,7 +864,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R912139e06cfc4334"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7912bafa8f142b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1405,7 +1405,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4fc8405df4b44b04"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccbff2996eec4f5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1628,7 +1628,7 @@
       </x:c>
       <x:c r="B6" s="16" t="str">
         <x:f>'Skills'!C6</x:f>
-        <x:v>맹독 안개</x:v>
+        <x:v>맹독 늪</x:v>
       </x:c>
       <x:c r="C6" s="5" t="str">
         <x:v>미정</x:v>
@@ -1823,7 +1823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9efe7a4b140c4cc2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2101a43777c74708"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2033,7 +2033,7 @@
       </x:c>
       <x:c r="B6" s="16" t="str">
         <x:f>'Skills'!C6</x:f>
-        <x:v>맹독 안개</x:v>
+        <x:v>맹독 늪</x:v>
       </x:c>
       <x:c r="C6" s="9" t="n">
         <x:v>30</x:v>
@@ -2252,7 +2252,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R77fad7a1690a4689"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R422a35627e2648dc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4508,7 +4508,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18c402cd58564257"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0e724c77b5947fb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4837,7 +4837,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R488c3cb391bc44fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0294a0713b664c4a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5015,7 +5015,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27e6369b610a4dcc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f77bf989dcb433c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5210,7 +5210,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra6882e447a3e4987"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R774af23012b741fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Re32e84b2bce343ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R7e85d5c0db3a4613"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R8a02e866d6fb41da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R4ea15bbc3c7c46b3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R91ce146a850c4c4d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R4c4b104688a949c9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R2bfd5c4faade442e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R6f00d504520941a7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rd3e087a157ec40d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R81dbcc681f6a44d2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R6149853889ba41a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R9ab34a80bdb54e67"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="Re554c98a7e904d26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R324efd102463456b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rd777cf03eb074eca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R076e2cb4d77c4608"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Mage_Skills" displayName="Mage_Skills" ref="A1:I11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="Mage_Skills" displayName="Mage_Skills" ref="A1:I10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="9">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="Key"/>
@@ -215,7 +215,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Mage_Parameters" displayName="Mage_Parameters" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="Mage_Parameters" displayName="Mage_Parameters" ref="A1:O10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="15">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="Key"/>
@@ -238,7 +238,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Mage_Bloom" displayName="Mage_Bloom" ref="A1:N11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="11" name="Mage_Bloom" displayName="Mage_Bloom" ref="A1:N10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="14">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="스킬"/>
@@ -260,7 +260,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Mage_Acquisition" displayName="Mage_Acquisition" ref="A1:J11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="Mage_Acquisition" displayName="Mage_Acquisition" ref="A1:J10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="스킬"/>
@@ -294,7 +294,7 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="Mage_Assets" displayName="Mage_Assets" ref="A1:J11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Mage_Assets" displayName="Mage_Assets" ref="A1:J10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="Key"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Mage_Targeting" displayName="Mage_Targeting" ref="A1:D11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="Mage_Targeting" displayName="Mage_Targeting" ref="A1:D10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="지점 선택"/>
@@ -747,124 +747,106 @@
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
       <x:c r="A8" s="9" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="5" t="str">
+        <x:v>Sanctuary</x:v>
+      </x:c>
+      <x:c r="C8" s="5" t="str">
+        <x:v>회복의 성역</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>생존 지원</x:v>
+      </x:c>
+      <x:c r="E8" s="9" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="F8" s="9" t="n">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G8" s="9" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="B8" s="5" t="str">
-        <x:v>GaleBlades</x:v>
-      </x:c>
-      <x:c r="C8" s="5" t="str">
-        <x:v>질풍 칼날</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>관통 파동</x:v>
-      </x:c>
-      <x:c r="E8" s="9" t="n">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="F8" s="9" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G8" s="9" t="n">
-        <x:v>2</x:v>
-      </x:c>
       <x:c r="H8" s="9" t="n">
-        <x:v>5</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I8" s="5" t="str">
-        <x:v>바람 칼날이 일직선으로 날아가 경로상의 적을 관통합니다.</x:v>
+        <x:v>성역을 펼쳐 범위 안에서 체력 비율이 가장 낮은 왕국군을 반복해서 회복합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>Sanctuary</x:v>
+        <x:v>Meteor</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>회복의 성역</x:v>
+        <x:v>운석 낙하</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>생존 지원</x:v>
+        <x:v>예고 폭발</x:v>
       </x:c>
       <x:c r="E9" s="9" t="n">
-        <x:v>45</x:v>
+        <x:v>260</x:v>
       </x:c>
       <x:c r="F9" s="9" t="n">
-        <x:v>18</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G9" s="9" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H9" s="9" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H9" s="9" t="n">
-        <x:v>3</x:v>
-      </x:c>
       <x:c r="I9" s="5" t="str">
-        <x:v>성역을 펼쳐 범위 안에서 체력 비율이 가장 낮은 왕국군을 반복해서 회복합니다.</x:v>
+        <x:v>운석을 떨어뜨려 주변 적을 공격합니다. 착탄 지점의 잔열이 두 번 더 피해를 줍니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>Meteor</x:v>
+        <x:v>VoidRift</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>운석 낙하</x:v>
+        <x:v>공허 균열</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>예고 폭발</x:v>
+        <x:v>흡인과 붕괴</x:v>
       </x:c>
       <x:c r="E10" s="9" t="n">
-        <x:v>260</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="F10" s="9" t="n">
-        <x:v>16</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G10" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H10" s="9" t="n">
         <x:v>6</x:v>
       </x:c>
       <x:c r="I10" s="5" t="str">
-        <x:v>운석을 떨어뜨려 주변 적을 공격합니다. 남은 불길이 두 번 더 피해를 줍니다.</x:v>
+        <x:v>균열보다 50% 넓은 범위의 적을 끌어당깁니다. 균열 안에서 지속 피해를 주고 닫힐 때 폭발합니다. 보스는 끌어당기지 못합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="70" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>VoidRift</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>공허 균열</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>흡인과 붕괴</x:v>
-      </x:c>
-      <x:c r="E11" s="9" t="n">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H11" s="9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str">
-        <x:v>적이 모인 곳의 허공에 원형 균열을 엽니다. 균열 안의 적을 중심으로 끌어당기며 지속 피해를 주고, 닫힐 때 폭발합니다. 보스는 끌어당기지 못합니다.</x:v>
-      </x:c>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="9"/>
+      <x:c r="F11" s="9"/>
+      <x:c r="G11" s="9"/>
+      <x:c r="H11" s="9"/>
+      <x:c r="I11" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7912bafa8f142b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8afb544d4874fde"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -984,7 +966,7 @@
       <x:c r="N2" s="5" t="str">
         <x:v>Lightning_SFX</x:v>
       </x:c>
-      <x:c r="O2" s="5" t="str"/>
+      <x:c r="O2" s="5"/>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="9" t="n">
@@ -1030,7 +1012,7 @@
       <x:c r="N3" s="5" t="str">
         <x:v>Ice_Spike_SFX</x:v>
       </x:c>
-      <x:c r="O3" s="5" t="str"/>
+      <x:c r="O3" s="5"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="9" t="n">
@@ -1124,7 +1106,7 @@
       <x:c r="N5" s="5" t="str">
         <x:v>Charge_Shot_SFX</x:v>
       </x:c>
-      <x:c r="O5" s="5" t="str"/>
+      <x:c r="O5" s="5"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="9" t="n">
@@ -1170,7 +1152,7 @@
       <x:c r="N6" s="5" t="str">
         <x:v>Water_Splash_SFX</x:v>
       </x:c>
-      <x:c r="O6" s="5" t="str"/>
+      <x:c r="O6" s="5"/>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="9" t="n">
@@ -1216,24 +1198,24 @@
       <x:c r="N7" s="5" t="str">
         <x:v>Ice_Block_SFX</x:v>
       </x:c>
-      <x:c r="O7" s="5" t="str"/>
+      <x:c r="O7" s="5"/>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
         <x:f>'Skills'!B8</x:f>
-        <x:v>GaleBlades</x:v>
+        <x:v>Sanctuary</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>0.550000011920929</x:v>
+        <x:v>1.899999976158142</x:v>
       </x:c>
       <x:c r="D8" s="18" t="n">
-        <x:v>0.800000011920929</x:v>
+        <x:v>4.199999809265137</x:v>
       </x:c>
       <x:c r="E8" s="18" t="n">
-        <x:v>0.4000000059604645</x:v>
+        <x:v>0.699999988079071</x:v>
       </x:c>
       <x:c r="F8" s="18" t="n">
         <x:v>0</x:v>
@@ -1245,7 +1227,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="I8" s="17" t="b">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="J8" s="5" t="str">
         <x:v>A4/A8 타격 수 보너스</x:v>
@@ -1260,26 +1242,26 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N8" s="5" t="str">
-        <x:v>Slash_Attack_SFX</x:v>
-      </x:c>
-      <x:c r="O8" s="5" t="str"/>
+        <x:v>Parrying_SFX</x:v>
+      </x:c>
+      <x:c r="O8" s="5"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
         <x:f>'Skills'!B9</x:f>
-        <x:v>Sanctuary</x:v>
+        <x:v>Meteor</x:v>
       </x:c>
       <x:c r="C9" s="18" t="n">
-        <x:v>1.899999976158142</x:v>
+        <x:v>1.5499999523162842</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
-        <x:v>4.199999809265137</x:v>
+        <x:v>0.800000011920929</x:v>
       </x:c>
       <x:c r="E9" s="18" t="n">
-        <x:v>0.699999988079071</x:v>
+        <x:v>0.800000011920929</x:v>
       </x:c>
       <x:c r="F9" s="18" t="n">
         <x:v>0</x:v>
@@ -1288,16 +1270,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="H9" s="18" t="n">
+        <x:v>0.13461539149284363</x:v>
+      </x:c>
+      <x:c r="I9" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="b">
-        <x:v>1</x:v>
-      </x:c>
       <x:c r="J9" s="5" t="str">
-        <x:v>A4/A8 타격 수 보너스</x:v>
+        <x:v>충돌 1회 + 잔열 2회</x:v>
       </x:c>
       <x:c r="K9" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="9" t="n">
         <x:v>100</x:v>
@@ -1306,44 +1288,44 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N9" s="5" t="str">
-        <x:v>Parrying_SFX</x:v>
-      </x:c>
-      <x:c r="O9" s="5" t="str"/>
+        <x:v>Fire_Tornado_SFX</x:v>
+      </x:c>
+      <x:c r="O9" s="5"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
         <x:f>'Skills'!B10</x:f>
-        <x:v>Meteor</x:v>
+        <x:v>VoidRift</x:v>
       </x:c>
       <x:c r="C10" s="18" t="n">
-        <x:v>1.5499999523162842</x:v>
+        <x:v>1.2999999523162842</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
-        <x:v>0.800000011920929</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E10" s="18" t="n">
-        <x:v>0.800000011920929</x:v>
+        <x:v>0.6000000238418579</x:v>
       </x:c>
       <x:c r="F10" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>0.8500000238418579</x:v>
       </x:c>
       <x:c r="G10" s="18" t="n">
-        <x:v>0</x:v>
+        <x:v>0.20000000298023224</x:v>
       </x:c>
       <x:c r="H10" s="18" t="n">
-        <x:v>0.13461539149284363</x:v>
+        <x:v>4.285714149475098</x:v>
       </x:c>
       <x:c r="I10" s="17" t="b">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J10" s="5" t="str">
-        <x:v>충돌 1회 + 잔불 2회</x:v>
+        <x:v>반복 피해 + 마지막 붕괴</x:v>
       </x:c>
       <x:c r="K10" s="9" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="L10" s="9" t="n">
         <x:v>100</x:v>
@@ -1352,60 +1334,31 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="N10" s="5" t="str">
-        <x:v>Fire_Tornado_SFX</x:v>
-      </x:c>
-      <x:c r="O10" s="5" t="str"/>
+        <x:v>Charge_Shot_SFX</x:v>
+      </x:c>
+      <x:c r="O10" s="5"/>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:f>'Skills'!B11</x:f>
-        <x:v>VoidRift</x:v>
-      </x:c>
-      <x:c r="C11" s="18" t="n">
-        <x:v>1.2999999523162842</x:v>
-      </x:c>
-      <x:c r="D11" s="18" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E11" s="18" t="n">
-        <x:v>0.6000000238418579</x:v>
-      </x:c>
-      <x:c r="F11" s="18" t="n">
-        <x:v>0.8500000238418579</x:v>
-      </x:c>
-      <x:c r="G11" s="18" t="n">
-        <x:v>0.20000000298023224</x:v>
-      </x:c>
-      <x:c r="H11" s="18" t="n">
-        <x:v>4.285714149475098</x:v>
-      </x:c>
-      <x:c r="I11" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J11" s="5" t="str">
-        <x:v>반복 피해 + 마지막 붕괴</x:v>
-      </x:c>
-      <x:c r="K11" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="L11" s="9" t="n">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="M11" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="N11" s="5" t="str">
-        <x:v>Charge_Shot_SFX</x:v>
-      </x:c>
-      <x:c r="O11" s="5" t="str"/>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="18"/>
+      <x:c r="D11" s="18"/>
+      <x:c r="E11" s="18"/>
+      <x:c r="F11" s="18"/>
+      <x:c r="G11" s="18"/>
+      <x:c r="H11" s="18"/>
+      <x:c r="I11" s="9"/>
+      <x:c r="J11" s="5"/>
+      <x:c r="K11" s="9"/>
+      <x:c r="L11" s="9"/>
+      <x:c r="M11" s="9"/>
+      <x:c r="N11" s="5"/>
+      <x:c r="O11" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rccbff2996eec4f5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56ffb972778641fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1690,17 +1643,17 @@
     </x:row>
     <x:row r="8" ht="90" customHeight="1">
       <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
         <x:f>'Skills'!C8</x:f>
-        <x:v>질풍 칼날</x:v>
+        <x:v>회복의 성역</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
         <x:v>미정</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>피해량 +15%. 전용 효과는 준비 중입니다.</x:v>
+        <x:v>회복량 +15%. 전용 효과는 준비 중입니다.</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
         <x:v>10</x:v>
@@ -1723,17 +1676,17 @@
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
         <x:f>'Skills'!C9</x:f>
-        <x:v>회복의 성역</x:v>
+        <x:v>운석 낙하</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>미정</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>회복량 +15%. 전용 효과는 준비 중입니다.</x:v>
+        <x:v>피해량 +15%. 전용 효과는 준비 중입니다.</x:v>
       </x:c>
       <x:c r="E9" s="9" t="n">
         <x:v>10</x:v>
@@ -1756,11 +1709,11 @@
     </x:row>
     <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
         <x:f>'Skills'!C10</x:f>
-        <x:v>운석 낙하</x:v>
+        <x:v>공허 균열</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
         <x:v>미정</x:v>
@@ -1788,32 +1741,15 @@
       <x:c r="N10" s="5"/>
     </x:row>
     <x:row r="11" ht="90" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:f>'Skills'!C11</x:f>
-        <x:v>공허 균열</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>미정</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>피해량 +15%. 전용 효과는 준비 중입니다.</x:v>
-      </x:c>
-      <x:c r="E11" s="9" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F11" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="G11" s="9" t="n">
-        <x:v>1.149999976158142</x:v>
-      </x:c>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="9"/>
+      <x:c r="F11" s="9"/>
+      <x:c r="G11" s="9"/>
       <x:c r="H11" s="5"/>
-      <x:c r="I11" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
+      <x:c r="I11" s="9"/>
       <x:c r="J11" s="5"/>
       <x:c r="K11" s="5"/>
       <x:c r="L11" s="5"/>
@@ -1823,7 +1759,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2101a43777c74708"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fdcf6085a9147f3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1891,7 +1827,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E2" s="9" t="n">
         <x:v>55</x:v>
@@ -1902,18 +1838,18 @@
       </x:c>
       <x:c r="G2" s="20" t="n">
         <x:f>F2/D2</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H2" s="20" t="n">
         <x:f>(F2+1)/D2</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I2" s="20" t="n">
         <x:f>H2/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J2" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -1928,7 +1864,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E3" s="9" t="n">
         <x:v>55</x:v>
@@ -1939,18 +1875,18 @@
       </x:c>
       <x:c r="G3" s="20" t="n">
         <x:f>F3/D3</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H3" s="20" t="n">
         <x:f>(F3+1)/D3</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I3" s="20" t="n">
         <x:f>H3/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J3" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -1965,7 +1901,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E4" s="9" t="n">
         <x:v>55</x:v>
@@ -1976,18 +1912,18 @@
       </x:c>
       <x:c r="G4" s="20" t="n">
         <x:f>F4/D4</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H4" s="20" t="n">
         <x:f>(F4+1)/D4</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I4" s="20" t="n">
         <x:f>H4/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J4" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -2002,7 +1938,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
         <x:v>55</x:v>
@@ -2013,18 +1949,18 @@
       </x:c>
       <x:c r="G5" s="20" t="n">
         <x:f>F5/D5</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H5" s="20" t="n">
         <x:f>(F5+1)/D5</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I5" s="20" t="n">
         <x:f>H5/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J5" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -2039,7 +1975,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E6" s="9" t="n">
         <x:v>55</x:v>
@@ -2050,18 +1986,18 @@
       </x:c>
       <x:c r="G6" s="20" t="n">
         <x:f>F6/D6</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H6" s="20" t="n">
         <x:f>(F6+1)/D6</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I6" s="20" t="n">
         <x:f>H6/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J6" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -2076,7 +2012,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E7" s="9" t="n">
         <x:v>55</x:v>
@@ -2087,33 +2023,33 @@
       </x:c>
       <x:c r="G7" s="20" t="n">
         <x:f>F7/D7</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H7" s="20" t="n">
         <x:f>(F7+1)/D7</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I7" s="20" t="n">
         <x:f>H7/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J7" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
         <x:f>'Skills'!C8</x:f>
-        <x:v>질풍 칼날</x:v>
+        <x:v>회복의 성역</x:v>
       </x:c>
       <x:c r="C8" s="9" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
         <x:v>55</x:v>
@@ -2124,33 +2060,33 @@
       </x:c>
       <x:c r="G8" s="20" t="n">
         <x:f>F8/D8</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H8" s="20" t="n">
         <x:f>(F8+1)/D8</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I8" s="20" t="n">
         <x:f>H8/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J8" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
         <x:f>'Skills'!C9</x:f>
-        <x:v>회복의 성역</x:v>
+        <x:v>운석 낙하</x:v>
       </x:c>
       <x:c r="C9" s="9" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E9" s="9" t="n">
         <x:v>55</x:v>
@@ -2161,33 +2097,33 @@
       </x:c>
       <x:c r="G9" s="20" t="n">
         <x:f>F9/D9</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H9" s="20" t="n">
         <x:f>(F9+1)/D9</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I9" s="20" t="n">
         <x:f>H9/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J9" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
         <x:f>'Skills'!C10</x:f>
-        <x:v>운석 낙하</x:v>
+        <x:v>공허 균열</x:v>
       </x:c>
       <x:c r="C10" s="9" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="19" t="n">
-        <x:v>0.05</x:v>
+        <x:v>0.05555555555555555</x:v>
       </x:c>
       <x:c r="E10" s="9" t="n">
         <x:v>55</x:v>
@@ -2198,61 +2134,36 @@
       </x:c>
       <x:c r="G10" s="20" t="n">
         <x:f>F10/D10</x:f>
-        <x:v>40</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="H10" s="20" t="n">
         <x:f>(F10+1)/D10</x:f>
-        <x:v>60</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="I10" s="20" t="n">
         <x:f>H10/21</x:f>
-        <x:v>2.857142857142857</x:v>
+        <x:v>2.5714285714285716</x:v>
       </x:c>
       <x:c r="J10" s="9" t="n">
-        <x:v>105</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:f>'Skills'!C11</x:f>
-        <x:v>공허 균열</x:v>
-      </x:c>
-      <x:c r="C11" s="9" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D11" s="19" t="n">
-        <x:v>0.05</x:v>
-      </x:c>
-      <x:c r="E11" s="9" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F11" s="5" t="n">
-        <x:f>ROUNDUP(E11/C11,0)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G11" s="20" t="n">
-        <x:f>F11/D11</x:f>
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="H11" s="20" t="n">
-        <x:f>(F11+1)/D11</x:f>
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="I11" s="20" t="n">
-        <x:f>H11/21</x:f>
-        <x:v>2.857142857142857</x:v>
-      </x:c>
-      <x:c r="J11" s="9" t="n">
-        <x:v>105</x:v>
-      </x:c>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="9"/>
+      <x:c r="D11" s="19"/>
+      <x:c r="E11" s="9"/>
+      <x:c r="F11" s="5"/>
+      <x:c r="G11" s="20"/>
+      <x:c r="H11" s="20"/>
+      <x:c r="I11" s="20"/>
+      <x:c r="J11" s="9"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R422a35627e2648dc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf66936d1f6954a4f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4508,7 +4419,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0e724c77b5947fb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8363c378f7ec4707"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4584,8 +4495,8 @@
       <x:c r="F2" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/Lightning.prefab</x:v>
       </x:c>
-      <x:c r="G2" s="5" t="str"/>
-      <x:c r="H2" s="5" t="str"/>
+      <x:c r="G2" s="5"/>
+      <x:c r="H2" s="5"/>
       <x:c r="I2" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/LightningBloomStrike.prefab</x:v>
       </x:c>
@@ -4613,8 +4524,8 @@
       <x:c r="F3" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/IceSpike.prefab</x:v>
       </x:c>
-      <x:c r="G3" s="5" t="str"/>
-      <x:c r="H3" s="5" t="str"/>
+      <x:c r="G3" s="5"/>
+      <x:c r="H3" s="5"/>
       <x:c r="I3" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/IceBloomCrystal.prefab</x:v>
       </x:c>
@@ -4642,10 +4553,10 @@
       <x:c r="F4" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/FireTornado.prefab</x:v>
       </x:c>
-      <x:c r="G4" s="5" t="str"/>
-      <x:c r="H4" s="5" t="str"/>
-      <x:c r="I4" s="5" t="str"/>
-      <x:c r="J4" s="5" t="str"/>
+      <x:c r="G4" s="5"/>
+      <x:c r="H4" s="5"/>
+      <x:c r="I4" s="5"/>
+      <x:c r="J4" s="5"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="9" t="n">
@@ -4667,12 +4578,12 @@
       <x:c r="F5" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/ArcaneVolley.prefab</x:v>
       </x:c>
-      <x:c r="G5" s="5" t="str"/>
+      <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/ArcaneImpact.prefab</x:v>
       </x:c>
-      <x:c r="I5" s="5" t="str"/>
-      <x:c r="J5" s="5" t="str"/>
+      <x:c r="I5" s="5"/>
+      <x:c r="J5" s="5"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="9" t="n">
@@ -4694,10 +4605,10 @@
       <x:c r="F6" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/VenomMist.prefab</x:v>
       </x:c>
-      <x:c r="G6" s="5" t="str"/>
-      <x:c r="H6" s="5" t="str"/>
-      <x:c r="I6" s="5" t="str"/>
-      <x:c r="J6" s="5" t="str"/>
+      <x:c r="G6" s="5"/>
+      <x:c r="H6" s="5"/>
+      <x:c r="I6" s="5"/>
+      <x:c r="J6" s="5"/>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="9" t="n">
@@ -4722,122 +4633,109 @@
       <x:c r="G7" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/GroundTelegraph.prefab</x:v>
       </x:c>
-      <x:c r="H7" s="5" t="str"/>
-      <x:c r="I7" s="5" t="str"/>
-      <x:c r="J7" s="5" t="str"/>
+      <x:c r="H7" s="5"/>
+      <x:c r="I7" s="5"/>
+      <x:c r="J7" s="5"/>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
         <x:f>'Skills'!B8</x:f>
-        <x:v>GaleBlades</x:v>
+        <x:v>Sanctuary</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>Assets/MageTower/SO/GaleBlades/MageTowerSkill_GaleBlades.asset</x:v>
+        <x:v>Assets/MageTower/SO/Sanctuary/MageTowerSkill_Sanctuary.asset</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/GaleBlades.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/Sanctuary.png</x:v>
       </x:c>
       <x:c r="E8" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/GaleBlades_Bloom.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/Sanctuary_Bloom.png</x:v>
       </x:c>
       <x:c r="F8" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/GaleBlades.prefab</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="str"/>
-      <x:c r="H8" s="5" t="str"/>
-      <x:c r="I8" s="5" t="str"/>
-      <x:c r="J8" s="5" t="str"/>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/Sanctuary.prefab</x:v>
+      </x:c>
+      <x:c r="G8" s="5"/>
+      <x:c r="H8" s="5" t="str">
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/SanctuaryHeal.prefab</x:v>
+      </x:c>
+      <x:c r="I8" s="5"/>
+      <x:c r="J8" s="5"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="16" t="str">
         <x:f>'Skills'!B9</x:f>
-        <x:v>Sanctuary</x:v>
+        <x:v>Meteor</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>Assets/MageTower/SO/Sanctuary/MageTowerSkill_Sanctuary.asset</x:v>
+        <x:v>Assets/MageTower/SO/Meteor/MageTowerSkill_Meteor.asset</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/Sanctuary.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/Meteor.png</x:v>
       </x:c>
       <x:c r="E9" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/Sanctuary_Bloom.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/Meteor_Bloom.png</x:v>
       </x:c>
       <x:c r="F9" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/Sanctuary.prefab</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="str"/>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="str">
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/GroundTelegraph.prefab</x:v>
+      </x:c>
       <x:c r="H9" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/SanctuaryHeal.prefab</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str"/>
-      <x:c r="J9" s="5" t="str"/>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
+      </x:c>
+      <x:c r="I9" s="5"/>
+      <x:c r="J9" s="5"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="16" t="str">
         <x:f>'Skills'!B10</x:f>
-        <x:v>Meteor</x:v>
+        <x:v>VoidRift</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>Assets/MageTower/SO/Meteor/MageTowerSkill_Meteor.asset</x:v>
+        <x:v>Assets/MageTower/SO/VoidRift/MageTowerSkill_VoidRift.asset</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/Meteor.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/VoidRift.png</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/Meteor_Bloom.png</x:v>
+        <x:v>Assets/_Project/Art/Icons/MageTower/VoidRift_Bloom.png</x:v>
       </x:c>
       <x:c r="F10" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/GroundTelegraph.prefab</x:v>
-      </x:c>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/VoidRift.prefab</x:v>
+      </x:c>
+      <x:c r="G10" s="5"/>
       <x:c r="H10" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str"/>
-      <x:c r="J10" s="5" t="str"/>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/VoidCollapse.prefab</x:v>
+      </x:c>
+      <x:c r="I10" s="5"/>
+      <x:c r="J10" s="5"/>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="str">
-        <x:f>'Skills'!B11</x:f>
-        <x:v>VoidRift</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>Assets/MageTower/SO/VoidRift/MageTowerSkill_VoidRift.asset</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/VoidRift.png</x:v>
-      </x:c>
-      <x:c r="E11" s="5" t="str">
-        <x:v>Assets/_Project/Art/Icons/MageTower/VoidRift_Bloom.png</x:v>
-      </x:c>
-      <x:c r="F11" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/VoidRift.prefab</x:v>
-      </x:c>
-      <x:c r="G11" s="5" t="str"/>
-      <x:c r="H11" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/VoidCollapse.prefab</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str"/>
-      <x:c r="J11" s="5" t="str"/>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="16"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
+      <x:c r="E11" s="5"/>
+      <x:c r="F11" s="5"/>
+      <x:c r="G11" s="5"/>
+      <x:c r="H11" s="5"/>
+      <x:c r="I11" s="5"/>
+      <x:c r="J11" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0294a0713b664c4a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f47310ac26043f9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4957,65 +4855,56 @@
     </x:row>
     <x:row r="8" ht="76" customHeight="1">
       <x:c r="A8" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>유효 표적 방향으로 관통 경로 설정</x:v>
+        <x:v>생존 아군 중 HP 비율 최저</x:v>
       </x:c>
       <x:c r="C8" s="5" t="str">
-        <x:v>파동이 실제 통과한 경로 안 최대 5체 · 파동당 같은 적 1회</x:v>
+        <x:v>매 회복마다 대상 재선정</x:v>
       </x:c>
       <x:c r="D8" s="5" t="str">
-        <x:v>단발 파동 전면</x:v>
+        <x:v>한 번 등장 후 지속시간 동안 회복 파동. 종료 시 한 번 퇴장</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" s="9" t="n">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="5" t="str">
-        <x:v>생존 아군 중 HP 비율 최저</x:v>
+        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>매 회복마다 대상 재선정</x:v>
+        <x:v>예고 위치 고정 · 충돌 후 잔열 2회</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
-        <x:v>성역 후면 · 회복 반짝임 전면</x:v>
+        <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="76" customHeight="1">
       <x:c r="A10" s="9" t="n">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B10" s="5" t="str">
-        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
+        <x:v>공중 균열, 피해 반경 1.3, 흡입 반경 1.95 월드 단위</x:v>
       </x:c>
       <x:c r="C10" s="5" t="str">
-        <x:v>예고 위치 고정 · 충돌 후 잔불 2회</x:v>
+        <x:v>흡입은 보이는 균열보다 50% 넓게 적용. 피해·붕괴 반경 유지</x:v>
       </x:c>
       <x:c r="D10" s="5" t="str">
-        <x:v>운석과 폭발 전면 · 잔불 후면</x:v>
+        <x:v>지속 균열 후면 · 붕괴 전면</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="76" customHeight="1">
-      <x:c r="A11" s="9" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="5" t="str">
-        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
-      </x:c>
-      <x:c r="C11" s="5" t="str">
-        <x:v>허공 원 안 몸체 중심만 흡인 · 보스 흡인 면역
-약한 감속으로 기존 강한 감속을 덮어쓰지 않음</x:v>
-      </x:c>
-      <x:c r="D11" s="5" t="str">
-        <x:v>지속 균열 후면 · 붕괴 전면</x:v>
-      </x:c>
+      <x:c r="A11" s="9"/>
+      <x:c r="B11" s="5"/>
+      <x:c r="C11" s="5"/>
+      <x:c r="D11" s="5"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f77bf989dcb433c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f445c770e24027"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5076,7 +4965,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.10.2 · 스킬 데이터 계약 mage-3 · 스킬 ID 0~9와 기존 에셋 GUID를 유지합니다.</x:v>
+        <x:v>게임 0.12.0. 스킬 데이터 계약 mage-4. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -5092,7 +4981,7 @@
         <x:v>공통 성장</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>직접 강화 E는 비전 지식으로 0~100, 각성 A는 동일 스킬 파편으로 0~10. A4/A8에 각각 1회 추가(화염 회오리는 2틱), A마다 효과량 +5%와 쿨타임 -2%. 운석은 고정 1회 충돌과 잔불 2회이며 타격 수 보너스를 사용하지 않습니다.</x:v>
+        <x:v>직접 강화 E는 비전 지식으로 0~100, 각성 A는 동일 스킬 파편으로 0~10. A4/A8에 각각 1회 추가(화염 회오리는 2틱), A마다 효과량 +5%와 쿨타임 -2%. 운석은 고정 1회 충돌과 잔열 2회이며 타격 수 보너스를 사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -5116,7 +5005,7 @@
         <x:v>확률</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>전체 뽑기는 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 스킬 10종은 등급 없이 각각 5%로 획득합니다. 희귀도는 장비에만 적용합니다.</x:v>
+        <x:v>전체 뽑기는 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 9종 스킬은 같은 확률(각 50%/9)입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -5132,7 +5021,7 @@
         <x:v>투자 기간</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>각성 누적55파편 기준입니다. 주당21회 전부 마탑에 사용하고 최초 보상·기존 파편을 제외하면 미보유 특정 스킬의 평균 개화 기간은 60회 뽑기, 약2.86주입니다. 장비 뽑기에 주화를 나누면 더 오래 걸립니다.</x:v>
+        <x:v>각성 누적 55파편. 주당 21회 마탑 뽑기 기준으로 미보유 특정 스킬의 평균 개화 기간은 54회, 약 2.57주입니다. 기존 파편과 최초 보상은 제외합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
@@ -5140,7 +5029,7 @@
         <x:v>확률 편차</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Acquisition의 P90은 해당 횟수까지 약90%가 목표를 달성한다는 정확한 음이항 계산입니다. 스킬당105회(약5주). 천장과 기간 보장은 없으며 수 주는 평균 목표입니다.</x:v>
+        <x:v>Acquisition의 P90은 정확한 음이항 계산입니다. 스킬당 95회까지 약 90%가 목표를 달성합니다. 천장이나 기간 보장은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="84" customHeight="1">
@@ -5172,7 +5061,7 @@
         <x:v>타격 연출</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>타격 시점에 피해·피격 반응·효과음을 맞춥니다. 별빛은 겹쳐 낙하하고 운석은 충돌 후 잔불을 남깁니다. 기절과 감속은 독립 만료하며 감속은 합산하지 않고 가장 강한 효과만 적용합니다. 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
+        <x:v>타격 시점에 피해·피격 반응·효과음을 맞춥니다. 별빛은 겹쳐 낙하하고 운석은 충돌 후 잔열을 남깁니다. 기절과 감속은 독립 만료하며 감속은 합산하지 않고 가장 강한 효과만 적용합니다. 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="84" customHeight="1">
@@ -5204,13 +5093,13 @@
         <x:v>보류 개화</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
-        <x:v>천벌·만년빙정 외 8종은 개화 미정으로 표기합니다. 현재는 기존 피해 또는 회복의15% 증가만 적용하며 확정된 고유 개화로 오해하지 않도록 유지합니다.</x:v>
+        <x:v>천벌·만년빙정 외 7종은 개화 미정이며 피해 또는 회복량이 15% 증가합니다.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R774af23012b741fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865e0bac42044ae0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rd3e087a157ec40d0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R81dbcc681f6a44d2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R6149853889ba41a9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R9ab34a80bdb54e67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="Re554c98a7e904d26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R324efd102463456b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rd777cf03eb074eca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R076e2cb4d77c4608"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R5e66305b0bcb496e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="Rb07b744bbd4642af"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R776d650675f2476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R401851261137418d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R3b65024a75cd4b4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rbf1994a6156043d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rbfaf17bb1c8b4f4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R03c33789bfde4450"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0.0000"/>
   </x:numFmts>
-  <x:fonts count="7">
+  <x:fonts count="8">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -60,6 +60,10 @@
       <x:color rgb="FF206447"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="맑은 고딕"/>
+    </x:font>
   </x:fonts>
   <x:fills count="3">
     <x:fill>
@@ -80,7 +84,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="23">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -172,6 +176,10 @@
     </x:xf>
     <x:xf numFmtId="202" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -672,13 +680,13 @@
         <x:v>전장 낙하</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
-        <x:v>62</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="G5" s="9" t="n">
-        <x:v>6</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H5" s="9" t="n">
         <x:v>1</x:v>
@@ -742,7 +750,7 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="I7" s="5" t="str">
-        <x:v>바위를 연속으로 솟아올려 주변 적을 공격하고 1초간 기절시킵니다.</x:v>
+        <x:v>바위를 연속으로 솟아올려 주변 적을 공격하고 1.4초간 기절시킵니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="70" customHeight="1">
@@ -846,7 +854,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8afb544d4874fde"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd5c94c2e05400c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1074,10 +1082,10 @@
         <x:v>0.550000011920929</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
-        <x:v>1.3199999332427979</x:v>
+        <x:v>2.16</x:v>
       </x:c>
       <x:c r="E5" s="18" t="n">
-        <x:v>0.2199999988079071</x:v>
+        <x:v>0.12</x:v>
       </x:c>
       <x:c r="F5" s="18" t="n">
         <x:v>0</x:v>
@@ -1172,7 +1180,7 @@
         <x:v>0.44999998807907104</x:v>
       </x:c>
       <x:c r="F7" s="18" t="n">
-        <x:v>1</x:v>
+        <x:v>1.4</x:v>
       </x:c>
       <x:c r="G7" s="18" t="n">
         <x:v>0</x:v>
@@ -1209,7 +1217,7 @@
         <x:v>Sanctuary</x:v>
       </x:c>
       <x:c r="C8" s="18" t="n">
-        <x:v>1.899999976158142</x:v>
+        <x:v>2.6</x:v>
       </x:c>
       <x:c r="D8" s="18" t="n">
         <x:v>4.199999809265137</x:v>
@@ -1358,7 +1366,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56ffb972778641fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64be8cc0f0d948c1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1482,7 +1490,7 @@
       </x:c>
       <x:c r="D3" s="5" t="str">
         <x:v>여러 적: 송곳 8개를 두 번 생성합니다. 각각 피해 50%.
-적 하나: 거대 빙정으로 피해 650%와 기절 2초를 줍니다.</x:v>
+적 하나: 거대 빙정으로 피해 650%를 줍니다. 기절 효과는 없습니다.</x:v>
       </x:c>
       <x:c r="E3" s="9" t="n">
         <x:v>10</x:v>
@@ -1497,7 +1505,7 @@
         <x:v>0.5</x:v>
       </x:c>
       <x:c r="I3" s="9" t="n">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="J3" s="5"/>
       <x:c r="K3" s="9" t="n">
@@ -1759,7 +1767,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9fdcf6085a9147f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca17e19059f4c6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2163,7 +2171,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf66936d1f6954a4f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45dc047724e94985"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4419,7 +4427,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8363c378f7ec4707"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51c64b05cc414188"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4684,9 +4692,7 @@
       <x:c r="F9" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
       </x:c>
-      <x:c r="G9" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/GroundTelegraph.prefab</x:v>
-      </x:c>
+      <x:c r="G9" s="5" t="str"/>
       <x:c r="H9" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
       </x:c>
@@ -4735,7 +4741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f47310ac26043f9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcefa5d3d3c134401"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4819,7 +4825,7 @@
       </x:c>
       <x:c r="C5" s="5" t="str">
         <x:v>별빛은 비행 전반 70% 동안 대상을 추적한 뒤 낙하 지점을 확정
-0.22초 간격 · 비행 0.48초</x:v>
+0.12초 간격 · 18개 기본 낙하 · 비행 0.48초</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
         <x:v>낙하와 충돌 전면</x:v>
@@ -4875,7 +4881,7 @@
         <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>예고 위치 고정 · 충돌 후 잔열 2회</x:v>
+        <x:v>착탄 지점 고정 · 시전 마법진 없음 · 충돌 후 잔열 2회</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
@@ -4904,7 +4910,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f445c770e24027"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15e8e26437e457a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4965,7 +4971,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.12.0. 스킬 데이터 계약 mage-4. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
+        <x:v>게임 0.13.0 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -5069,7 +5075,7 @@
         <x:v>외부 원본</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>ExternalAssets는 원본 저장소이며 직접 변경하지 않습니다. Assets 탭의 작업본만 사용합니다. 생성 출처는 AI/comfyui/mage-skills/20260915, 20260916-combat 및 20260917-polish입니다. 운석 잔흔은 두 모델 비교 후 채택한 단일 64px·6색 지면 데칼입니다.</x:v>
+        <x:v>ExternalAssets 원본은 보존합니다. 최신 제작은 AI/comfyui/mage-vfx/revision1~4 및 finish-manifest.json에 실제 API·UI 그래프·원본·채택/기각·비용을 기록했습니다. 운석 시전 원과 지속 불길을 제거하고 크레이터를 축소했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
@@ -5096,10 +5102,58 @@
         <x:v>천벌·만년빙정 외 7종은 개화 미정이며 피해 또는 회복량이 15% 증가합니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="23" ht="68" customHeight="1">
+      <x:c r="A23" s="24" t="str">
+        <x:v>왕국군 공격 계수</x:v>
+      </x:c>
+      <x:c r="B23" s="24" t="str">
+        <x:v>시전당 1회 효과량 = round(기본 효과량×1.04^E×(1+0.05A)) + round(출전 3인 ATK 합×기본 효과량/400×(1+0.005E+0.025A)). 사망한 출전 병사도 합산하고 시전 시작 시 고정합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="68" customHeight="1">
+      <x:c r="A24" s="24" t="str">
+        <x:v>수동 시전</x:v>
+      </x:c>
+      <x:c r="B24" s="24" t="str">
+        <x:v>자동 OFF에서 우측 스테이지 표시 위에 장착 스킬을 나열합니다. ON이면 대응하는 퇴장 애니메이션. 준비 점등·시계 방향 쿨다운 음영·남은 초를 표시합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="68" customHeight="1">
+      <x:c r="A25" s="24" t="str">
+        <x:v>조준 구도</x:v>
+      </x:c>
+      <x:c r="B25" s="24" t="str">
+        <x:v>발 위치 기준 원형 게임 판정과 쿼터뷰 타원 장판 표시를 구분합니다. 분산 스킬인 얼음 송곳·유성우는 드래그 시전과 쿨다운 소비를 하지 않습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="68" customHeight="1">
+      <x:c r="A26" s="24" t="str">
+        <x:v>각성 안내</x:v>
+      </x:c>
+      <x:c r="B26" s="24" t="str">
+        <x:v>A4/A8 추가 타격·틱, 다음 각성의 효과량·쿨타임·타격 수, A10 개화 효과를 상세 화면에 표시합니다. 운석은 추가 타격 보너스가 없습니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="68" customHeight="1">
+      <x:c r="A27" s="24" t="str">
+        <x:v>성역 연출</x:v>
+      </x:c>
+      <x:c r="B27" s="24" t="str">
+        <x:v>반경 2.6. 한 번 상승한 불투명 문양을 유지하며 발밑 지면 파동으로 회복하고 종료 때 한 번 하강합니다.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="68" customHeight="1">
+      <x:c r="A28" s="24" t="str">
+        <x:v>픽셀과 레이어</x:v>
+      </x:c>
+      <x:c r="B28" s="24" t="str">
+        <x:v>핵심 VFX 목표 32px/월드 단위, 4~6색·Point·ASTC4×4. 단발 타격은 전면, 독 늪·잔열·흡인 등 지속 장판은 후면입니다. 이펙트가 큰 경우 원본 논리 해상도도 함께 높입니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R865e0bac42044ae0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R694d7a683991474e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R5e66305b0bcb496e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="Rb07b744bbd4642af"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R776d650675f2476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R401851261137418d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R3b65024a75cd4b4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rbf1994a6156043d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rbfaf17bb1c8b4f4f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R03c33789bfde4450"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rfb40bf9e195d4206"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R03eb3efe38804895"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R40cd25fdcdf5449d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R7b457e33fc184ea5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R8ac5e82532b24e9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rfb662544e7264b58"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R1a380916625e4f82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R4a0f847c16894ed3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -605,7 +605,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="5" t="str">
-        <x:v>같은 지점에 번개를 연속으로 내려 주변 적을 공격합니다.</x:v>
+        <x:v>번개를 3회 연속으로 내립니다. 4·8각성마다 같은 패턴의 낙뢰가 1회 추가됩니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="70" customHeight="1">
@@ -854,7 +854,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2bd5c94c2e05400c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R833b7bd22e084c3c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -942,10 +942,10 @@
         <x:v>0.550000011920929</x:v>
       </x:c>
       <x:c r="D2" s="18" t="n">
-        <x:v>0.9000000357627869</x:v>
+        <x:v>0.5</x:v>
       </x:c>
       <x:c r="E2" s="18" t="n">
-        <x:v>0.30000001192092896</x:v>
+        <x:v>0.16666666666666666</x:v>
       </x:c>
       <x:c r="F2" s="18" t="n">
         <x:v>0</x:v>
@@ -1366,7 +1366,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64be8cc0f0d948c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7174bf87fcb45a4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1767,7 +1767,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ca17e19059f4c6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8ffd66f2c145d4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2171,7 +2171,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45dc047724e94985"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55175084dd364b3e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4427,7 +4427,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51c64b05cc414188"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e3fe0e4ef14420"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4741,7 +4741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcefa5d3d3c134401"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7ef47ec0f942df"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4781,8 +4781,8 @@
         <x:v>적이 가장 많이 모인 지점</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>고정 원형 범위 · 천벌의 구름 높이와 벼락 길이는 상단 여백에 맞춤
-연출 높이 보정으로 타격 지점을 아래로 이동하지 않음</x:v>
+        <x:v>일반: 첫 중심 이후 0.8 이내 분산, 낙뢰마다 반경 0.55. 조준 반경 1.35.
+약 0.167초 간격으로 기본 3회, A4 4회, A8 이상 5회. 천벌 연출 유지.</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>즉발 낙뢰 전면 · 구름 전면</x:v>
@@ -4881,7 +4881,8 @@
         <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
       </x:c>
       <x:c r="C9" s="5" t="str">
-        <x:v>착탄 지점 고정 · 시전 마법진 없음 · 충돌 후 잔열 2회</x:v>
+        <x:v>착탄 지점 고정. 시전 마법진 없음.
+2.4초 가속 낙하, 접촉 후 0.09초에 피해. 잔열 2회.</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
@@ -4910,7 +4911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd15e8e26437e457a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb70d5060c364185"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4971,7 +4972,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.13.0 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
+        <x:v>게임 0.13.1 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -5075,7 +5076,7 @@
         <x:v>외부 원본</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>ExternalAssets 원본은 보존합니다. 최신 제작은 AI/comfyui/mage-vfx/revision1~4 및 finish-manifest.json에 실제 API·UI 그래프·원본·채택/기각·비용을 기록했습니다. 운석 시전 원과 지속 불길을 제거하고 크레이터를 축소했습니다.</x:v>
+        <x:v>ExternalAssets 원본은 보존합니다. 제작 출처: AI/comfyui/mage-vfx/revision1~5. 일반 라이트닝은 최초 ThunderEffects 원화 복원. 운석은 Comfy 표면 마스터를 회전·화염 흐름·파편 48프레임으로 가공했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
@@ -5153,7 +5154,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R694d7a683991474e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2372c9049dec47d1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rfb40bf9e195d4206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R03eb3efe38804895"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R40cd25fdcdf5449d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R7b457e33fc184ea5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R8ac5e82532b24e9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rfb662544e7264b58"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R1a380916625e4f82"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R4a0f847c16894ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rc98ca8b488ab43a8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R62aef14d353e4d9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="Rb654bd1f2e1a45ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R1af024dc59e64e53"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R375048e3161446f3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rcfbc5a9b1bad4e0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R185f5fb4a3294e29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R3011c7e3fdc546e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -854,7 +854,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R833b7bd22e084c3c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38de710b36ea451d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1366,7 +1366,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7174bf87fcb45a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79950523d99c4e5c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1767,7 +1767,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7b8ffd66f2c145d4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R805d4a9ac9714224"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2171,7 +2171,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R55175084dd364b3e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff2ded0646a4476"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4427,7 +4427,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e3fe0e4ef14420"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0139623cfc134fdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4741,7 +4741,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref7ef47ec0f942df"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5af9039f4114504"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4882,7 +4882,7 @@
       </x:c>
       <x:c r="C9" s="5" t="str">
         <x:v>착탄 지점 고정. 시전 마법진 없음.
-2.4초 가속 낙하, 접촉 후 0.09초에 피해. 잔열 2회.</x:v>
+1.5초 가속 낙하, 접촉 후 0.09초에 피해. 잔열 2회.</x:v>
       </x:c>
       <x:c r="D9" s="5" t="str">
         <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
@@ -4911,7 +4911,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb70d5060c364185"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbe0ed84f3b1414b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4972,7 +4972,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.13.1 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
+        <x:v>게임 0.13.2 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -5154,7 +5154,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2372c9049dec47d1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36db18132344b88"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="Rc98ca8b488ab43a8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R62aef14d353e4d9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="Rb654bd1f2e1a45ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R1af024dc59e64e53"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R375048e3161446f3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rcfbc5a9b1bad4e0f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R185f5fb4a3294e29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="R3011c7e3fdc546e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R2b25563ab4234517"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R252594dbfc684dd0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R9949f6ace02f4682"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R55d581f3c3644ed7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R0397ae5074cf4a68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rdcad8e5da80041fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rf4e5a5af546e4974"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="Rbdb279aa60c54caf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0.0000"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -64,8 +64,13 @@
       <x:sz val="11"/>
       <x:name val="맑은 고딕"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF6B7280"/>
+      <x:name val="Malgun Gothic"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -77,6 +82,11 @@
         <x:fgColor rgb="FF253E52"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -84,7 +94,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="25">
+  <x:cellXfs count="38">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -180,6 +190,55 @@
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="3" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -605,7 +664,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="I2" s="5" t="str">
-        <x:v>번개를 3회 연속으로 내립니다. 4·8각성마다 같은 패턴의 낙뢰가 1회 추가됩니다.</x:v>
+        <x:v>번개를 3회 연속으로 내립니다. 4·8각성마다 같은 패턴의 낙뢰가 1회 추가됩니다. 낙뢰 위치는 서로 간격을 두고 분산됩니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="70" customHeight="1">
@@ -677,7 +736,7 @@
         <x:v>유성우</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>전장 낙하</x:v>
+        <x:v>무작위 소범위 폭격</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
         <x:v>28</x:v>
@@ -689,10 +748,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="H5" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="I5" s="5" t="str">
-        <x:v>전장 곳곳의 적에게 별빛을 차례로 떨어뜨립니다. 별빛이 닿은 적에게 피해를 줍니다.</x:v>
+        <x:v>성역보다 조금 넓은 범위의 무작위 지점에 붉은 별빛을 떨어뜨립니다. 적을 추적하지 않으며 작은 착탄 파동 안에 범위 피해를 줍니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="70" customHeight="1">
@@ -783,32 +842,32 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>운석 낙하</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>예고 폭발</x:v>
-      </x:c>
-      <x:c r="E9" s="9" t="n">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="F9" s="9" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G9" s="9" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="9" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str">
-        <x:v>운석을 떨어뜨려 주변 적을 공격합니다. 착탄 지점의 잔열이 두 번 더 피해를 줍니다.</x:v>
+      <x:c r="C9" s="28" t="str">
+        <x:v>독립 운석 삭제</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="str">
+        <x:v>ID 3 개화로 통합</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="28" t="str">
+        <x:v>ID 8은 비활성 보존 ID입니다. 로스터·장착·뽑기에 나오지 않으며 유성우의 개화 메테오로 통합했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="70" customHeight="1">
@@ -854,7 +913,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R38de710b36ea451d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36a81b40f5f3428a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1255,50 +1314,50 @@
       <x:c r="O8" s="5"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:f>'Skills'!B9</x:f>
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="18" t="n">
+      <x:c r="C9" s="32" t="n">
         <x:v>1.5499999523162842</x:v>
       </x:c>
-      <x:c r="D9" s="18" t="n">
+      <x:c r="D9" s="32" t="n">
         <x:v>0.800000011920929</x:v>
       </x:c>
-      <x:c r="E9" s="18" t="n">
+      <x:c r="E9" s="32" t="n">
         <x:v>0.800000011920929</x:v>
       </x:c>
-      <x:c r="F9" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="18" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="18" t="n">
+      <x:c r="F9" s="32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="32" t="n">
         <x:v>0.13461539149284363</x:v>
       </x:c>
-      <x:c r="I9" s="17" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="5" t="str">
+      <x:c r="I9" s="33" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="28" t="str">
         <x:v>충돌 1회 + 잔열 2회</x:v>
       </x:c>
-      <x:c r="K9" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="9" t="n">
+      <x:c r="K9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="27" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="M9" s="9" t="n">
+      <x:c r="M9" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N9" s="5" t="str">
+      <x:c r="N9" s="28" t="str">
         <x:v>Fire_Tornado_SFX</x:v>
       </x:c>
-      <x:c r="O9" s="5"/>
+      <x:c r="O9" s="28"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -1366,7 +1425,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79950523d99c4e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a404bc63e948f8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1417,7 +1476,7 @@
         <x:v>PowerMultiplier</x:v>
       </x:c>
       <x:c r="H1" s="8" t="str">
-        <x:v>CrowdPerHitMultiplier</x:v>
+        <x:v>CrowdOrFieldTickMultiplier</x:v>
       </x:c>
       <x:c r="I1" s="8" t="str">
         <x:v>SingleTargetStunSec</x:v>
@@ -1550,7 +1609,7 @@
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
     </x:row>
-    <x:row r="5" ht="90" customHeight="1">
+    <x:row r="5" ht="110" customHeight="1">
       <x:c r="A5" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
@@ -1559,29 +1618,39 @@
         <x:v>유성우</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>미정</x:v>
+        <x:v>메테오</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>피해량 +15%. 전용 효과는 준비 중입니다.</x:v>
+        <x:v>거대한 운석이 1.5초 낙하해 피해 2000%를 줍니다.
+균열 장판이 3.5초 동안 0.5초마다 피해 200%를 주고, 안의 적을 60% 감속합니다.
+쿨타임 1.6배. 장판 밖에서는 약 0.12초 안에 감속이 해제되고 더 약한 기존 감속이 복구됩니다.</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="9" t="n">
-        <x:v>1</x:v>
+        <x:v>1.6</x:v>
       </x:c>
       <x:c r="G5" s="9" t="n">
-        <x:v>1.149999976158142</x:v>
-      </x:c>
-      <x:c r="H5" s="5"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="H5" s="5" t="n">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="I5" s="9" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J5" s="5"/>
+      <x:c r="J5" s="5" t="n">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="K5" s="5"/>
       <x:c r="L5" s="5"/>
-      <x:c r="M5" s="5"/>
-      <x:c r="N5" s="5"/>
+      <x:c r="M5" s="5" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
+      <x:c r="N5" s="5" t="n">
+        <x:v>1.75</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="90" customHeight="1">
       <x:c r="A6" s="9" t="n">
@@ -1683,37 +1752,37 @@
       <x:c r="N8" s="5"/>
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:f>'Skills'!C9</x:f>
-        <x:v>운석 낙하</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>미정</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>피해량 +15%. 전용 효과는 준비 중입니다.</x:v>
-      </x:c>
-      <x:c r="E9" s="9" t="n">
+        <x:v>독립 운석 삭제</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="str">
+        <x:v>통합됨</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="str">
+        <x:v>ID 3 메테오 개화 항목을 사용합니다.</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F9" s="9" t="n">
+      <x:c r="F9" s="27" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="9" t="n">
+      <x:c r="G9" s="27" t="n">
         <x:v>1.149999976158142</x:v>
       </x:c>
-      <x:c r="H9" s="5"/>
-      <x:c r="I9" s="9" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="5"/>
-      <x:c r="K9" s="5"/>
-      <x:c r="L9" s="5"/>
-      <x:c r="M9" s="5"/>
-      <x:c r="N9" s="5"/>
+      <x:c r="H9" s="28"/>
+      <x:c r="I9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="28"/>
+      <x:c r="K9" s="28"/>
+      <x:c r="L9" s="28"/>
+      <x:c r="M9" s="28"/>
+      <x:c r="N9" s="28"/>
     </x:row>
     <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -1767,7 +1836,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R805d4a9ac9714224"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49f09b68380e4338"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1835,7 +1904,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D2" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E2" s="9" t="n">
         <x:v>55</x:v>
@@ -1846,18 +1915,18 @@
       </x:c>
       <x:c r="G2" s="20" t="n">
         <x:f>F2/D2</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H2" s="20" t="n">
         <x:f>(F2+1)/D2</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I2" s="20" t="n">
         <x:f>H2/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J2" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
@@ -1872,7 +1941,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E3" s="9" t="n">
         <x:v>55</x:v>
@@ -1883,18 +1952,18 @@
       </x:c>
       <x:c r="G3" s="20" t="n">
         <x:f>F3/D3</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H3" s="20" t="n">
         <x:f>(F3+1)/D3</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I3" s="20" t="n">
         <x:f>H3/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J3" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
@@ -1909,7 +1978,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D4" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E4" s="9" t="n">
         <x:v>55</x:v>
@@ -1920,18 +1989,18 @@
       </x:c>
       <x:c r="G4" s="20" t="n">
         <x:f>F4/D4</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H4" s="20" t="n">
         <x:f>(F4+1)/D4</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I4" s="20" t="n">
         <x:f>H4/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J4" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
@@ -1946,7 +2015,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D5" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E5" s="9" t="n">
         <x:v>55</x:v>
@@ -1957,18 +2026,18 @@
       </x:c>
       <x:c r="G5" s="20" t="n">
         <x:f>F5/D5</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H5" s="20" t="n">
         <x:f>(F5+1)/D5</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I5" s="20" t="n">
         <x:f>H5/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J5" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
@@ -1983,7 +2052,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D6" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E6" s="9" t="n">
         <x:v>55</x:v>
@@ -1994,18 +2063,18 @@
       </x:c>
       <x:c r="G6" s="20" t="n">
         <x:f>F6/D6</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H6" s="20" t="n">
         <x:f>(F6+1)/D6</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I6" s="20" t="n">
         <x:f>H6/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J6" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
@@ -2020,7 +2089,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E7" s="9" t="n">
         <x:v>55</x:v>
@@ -2031,18 +2100,18 @@
       </x:c>
       <x:c r="G7" s="20" t="n">
         <x:f>F7/D7</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H7" s="20" t="n">
         <x:f>(F7+1)/D7</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I7" s="20" t="n">
         <x:f>H7/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J7" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
@@ -2057,7 +2126,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D8" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E8" s="9" t="n">
         <x:v>55</x:v>
@@ -2068,55 +2137,51 @@
       </x:c>
       <x:c r="G8" s="20" t="n">
         <x:f>F8/D8</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H8" s="20" t="n">
         <x:f>(F8+1)/D8</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I8" s="20" t="n">
         <x:f>H8/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J8" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:f>'Skills'!C9</x:f>
-        <x:v>운석 낙하</x:v>
-      </x:c>
-      <x:c r="C9" s="9" t="n">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D9" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
-      </x:c>
-      <x:c r="E9" s="9" t="n">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="n">
-        <x:f>ROUNDUP(E9/C9,0)</x:f>
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G9" s="20" t="n">
-        <x:f>F9/D9</x:f>
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="H9" s="20" t="n">
-        <x:f>(F9+1)/D9</x:f>
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="I9" s="20" t="n">
-        <x:f>H9/21</x:f>
-        <x:v>2.5714285714285716</x:v>
-      </x:c>
-      <x:c r="J9" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>독립 운석 삭제</x:v>
+      </x:c>
+      <x:c r="C9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="36" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="27" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
@@ -2131,7 +2196,7 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="19" t="n">
-        <x:v>0.05555555555555555</x:v>
+        <x:v>0.0625</x:v>
       </x:c>
       <x:c r="E10" s="9" t="n">
         <x:v>55</x:v>
@@ -2142,18 +2207,18 @@
       </x:c>
       <x:c r="G10" s="20" t="n">
         <x:f>F10/D10</x:f>
-        <x:v>36</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H10" s="20" t="n">
         <x:f>(F10+1)/D10</x:f>
-        <x:v>54</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I10" s="20" t="n">
         <x:f>H10/21</x:f>
-        <x:v>2.5714285714285716</x:v>
+        <x:v>2.2857142857142856</x:v>
       </x:c>
       <x:c r="J10" s="9" t="n">
-        <x:v>95</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
@@ -2171,7 +2236,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Reff2ded0646a4476"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e7c2d7649541c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4427,7 +4492,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0139623cfc134fdc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e861d794534565"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4449,6 +4514,7 @@
     <x:col min="8" max="8" width="86" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="86" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="88" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="88" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="46" customHeight="1">
@@ -4482,6 +4548,9 @@
       <x:c r="J1" s="8" t="str">
         <x:v>BloomCastingPrefabPath</x:v>
       </x:c>
+      <x:c r="K1" t="str">
+        <x:v>BloomSecondaryPrefabPath</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="34" customHeight="1">
       <x:c r="A2" s="9" t="n">
@@ -4511,6 +4580,7 @@
       <x:c r="J2" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/LightningBloomCloud.prefab</x:v>
       </x:c>
+      <x:c r="K2" t="str"/>
     </x:row>
     <x:row r="3" ht="34" customHeight="1">
       <x:c r="A3" s="9" t="n">
@@ -4540,6 +4610,7 @@
       <x:c r="J3" s="5" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/IceBloomWarning.prefab</x:v>
       </x:c>
+      <x:c r="K3" t="str"/>
     </x:row>
     <x:row r="4" ht="34" customHeight="1">
       <x:c r="A4" s="9" t="n">
@@ -4565,6 +4636,7 @@
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
+      <x:c r="K4" t="str"/>
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="9" t="n">
@@ -4588,10 +4660,15 @@
       </x:c>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5" t="str">
-        <x:v>Assets/_Project/Prefabs/VFX/MageTower/ArcaneImpact.prefab</x:v>
-      </x:c>
-      <x:c r="I5" s="5"/>
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/StarfallPulse.prefab</x:v>
+      </x:c>
+      <x:c r="I5" s="5" t="str">
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
+      </x:c>
       <x:c r="J5" s="5"/>
+      <x:c r="K5" t="str">
+        <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
+      </x:c>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
       <x:c r="A6" s="9" t="n">
@@ -4617,6 +4694,7 @@
       <x:c r="H6" s="5"/>
       <x:c r="I6" s="5"/>
       <x:c r="J6" s="5"/>
+      <x:c r="K6" t="str"/>
     </x:row>
     <x:row r="7" ht="34" customHeight="1">
       <x:c r="A7" s="9" t="n">
@@ -4644,6 +4722,7 @@
       <x:c r="H7" s="5"/>
       <x:c r="I7" s="5"/>
       <x:c r="J7" s="5"/>
+      <x:c r="K7" t="str"/>
     </x:row>
     <x:row r="8" ht="34" customHeight="1">
       <x:c r="A8" s="9" t="n">
@@ -4671,33 +4750,35 @@
       </x:c>
       <x:c r="I8" s="5"/>
       <x:c r="J8" s="5"/>
+      <x:c r="K8" t="str"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="16" t="str">
+      <x:c r="B9" s="28" t="str">
         <x:f>'Skills'!B9</x:f>
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="5" t="str">
+      <x:c r="C9" s="28" t="str">
         <x:v>Assets/MageTower/SO/Meteor/MageTowerSkill_Meteor.asset</x:v>
       </x:c>
-      <x:c r="D9" s="5" t="str">
+      <x:c r="D9" s="28" t="str">
         <x:v>Assets/_Project/Art/Icons/MageTower/Meteor.png</x:v>
       </x:c>
-      <x:c r="E9" s="5" t="str">
+      <x:c r="E9" s="28" t="str">
         <x:v>Assets/_Project/Art/Icons/MageTower/Meteor_Bloom.png</x:v>
       </x:c>
-      <x:c r="F9" s="5" t="str">
+      <x:c r="F9" s="28" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
       </x:c>
-      <x:c r="G9" s="5" t="str"/>
-      <x:c r="H9" s="5" t="str">
+      <x:c r="G9" s="28" t="str"/>
+      <x:c r="H9" s="28" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
       </x:c>
-      <x:c r="I9" s="5"/>
-      <x:c r="J9" s="5"/>
+      <x:c r="I9" s="28"/>
+      <x:c r="J9" s="28"/>
+      <x:c r="K9" t="str"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -4725,6 +4806,7 @@
       </x:c>
       <x:c r="I10" s="5"/>
       <x:c r="J10" s="5"/>
+      <x:c r="K10" t="str"/>
     </x:row>
     <x:row r="11" ht="34" customHeight="1">
       <x:c r="A11" s="9"/>
@@ -4741,7 +4823,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5af9039f4114504"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ec304716b734fa4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4781,8 +4863,8 @@
         <x:v>적이 가장 많이 모인 지점</x:v>
       </x:c>
       <x:c r="C2" s="5" t="str">
-        <x:v>일반: 첫 중심 이후 0.8 이내 분산, 낙뢰마다 반경 0.55. 조준 반경 1.35.
-약 0.167초 간격으로 기본 3회, A4 4회, A8 이상 5회. 천벌 연출 유지.</x:v>
+        <x:v>일반: 첫 중심 이후 1.15 이내 분산, 기존 낙뢰와 0.45 이상 간격을 우선 확보. 낙뢰마다 반경 0.55, 조준 반경 1.7.
+약 0.167초 간격으로 A0 3회, A4 4회, A8 5회. 매 타격 약한 흔들림, 천벌 타격 때 강한 흔들림.</x:v>
       </x:c>
       <x:c r="D2" s="5" t="str">
         <x:v>즉발 낙뢰 전면 · 구름 전면</x:v>
@@ -4816,19 +4898,21 @@
         <x:v>지속 장판 후면</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="76" customHeight="1">
+    <x:row r="5" ht="145" customHeight="1">
       <x:c r="A5" s="9" t="n">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B5" s="5" t="str">
-        <x:v>전장 내 적을 차례로 선택</x:v>
+        <x:v>전장 중심의 고정 타원 범위 · 적을 지정하거나 추적하지 않음</x:v>
       </x:c>
       <x:c r="C5" s="5" t="str">
-        <x:v>별빛은 비행 전반 70% 동안 대상을 추적한 뒤 낙하 지점을 확정
-0.12초 간격 · 18개 기본 낙하 · 비행 0.48초</x:v>
+        <x:v>기본: 반경 3, Y축 0.65배 타원 안 균등 난수. 18개/A4 19개/A8 20개, 0.12초 간격, 비행 0.48초.
+착탄 파동 반경 0.55(Y 0.65배), 최대 6체. 기본형 드래그 불가.
+메테오: 1.5초 낙하, 접촉 후 0.09초에 충돌 피해. 충돌 반경 1.75(Y 0.65배).
+장판 반경 1.25(Y 0.42배), 3.5초, 0.5초마다 피해 200%/총 7틱, 적 60% 감속. 메테오는 드래그 가능.</x:v>
       </x:c>
       <x:c r="D5" s="5" t="str">
-        <x:v>낙하와 충돌 전면</x:v>
+        <x:v>별빛·운석·폭발 전면 / 작은 파동·갈색 지면·붉은 균열 후면</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="76" customHeight="1">
@@ -4874,17 +4958,16 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="76" customHeight="1">
-      <x:c r="A9" s="9" t="n">
+      <x:c r="A9" s="27" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="5" t="str">
-        <x:v>적이 가장 많이 모인 지점 · 가장자리 안쪽 보정</x:v>
-      </x:c>
-      <x:c r="C9" s="5" t="str">
-        <x:v>착탄 지점 고정. 시전 마법진 없음.
-1.5초 가속 낙하, 접촉 후 0.09초에 피해. 잔열 2회.</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
+      <x:c r="B9" s="28" t="str">
+        <x:v>비활성 보존 ID</x:v>
+      </x:c>
+      <x:c r="C9" s="28" t="str">
+        <x:v>ID 3 기본 유성우 / 개화 메테오를 참조.</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="str">
         <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
       </x:c>
     </x:row>
@@ -4911,7 +4994,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbe0ed84f3b1414b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4399e50245884bf9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4972,7 +5055,7 @@
         <x:v>버전</x:v>
       </x:c>
       <x:c r="B6" s="5" t="str">
-        <x:v>게임 0.13.2 운영 개정 2026-09-20. 9종, ID 0–5·7–9. 삭제된 ID 6은 재사용하지 않습니다.</x:v>
+        <x:v>게임 0.14.0 운영 개정 2026-09-20. 활성 8종, ID 0–5·7·9. ID 6·8은 재사용하지 않습니다. 회색 ID 8 행은 통합 이력을 표시합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="62" customHeight="1">
@@ -4988,7 +5071,7 @@
         <x:v>공통 성장</x:v>
       </x:c>
       <x:c r="B8" s="5" t="str">
-        <x:v>직접 강화 E는 비전 지식으로 0~100, 각성 A는 동일 스킬 파편으로 0~10. A4/A8에 각각 1회 추가(화염 회오리는 2틱), A마다 효과량 +5%와 쿨타임 -2%. 운석은 고정 1회 충돌과 잔열 2회이며 타격 수 보너스를 사용하지 않습니다.</x:v>
+        <x:v>E 0~100은 비전 지식, A 0~10은 동일 스킬 파편. A4/A8 기본 타격 +1(화염 회오리 +2틱), A마다 효과량 +5%와 쿨타임 -2%. 메테오는 운석 1회와 3.5초 잔열로 고정됩니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="62" customHeight="1">
@@ -5012,7 +5095,7 @@
         <x:v>확률</x:v>
       </x:c>
       <x:c r="B11" s="5" t="str">
-        <x:v>전체 뽑기는 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 9종 스킬은 같은 확률(각 50%/9)입니다.</x:v>
+        <x:v>전체 스킬 50%, 비전 지식 10개 30%·20개 15%·50개 5%. 활성 8종은 각각 6.25%입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="62" customHeight="1">
@@ -5028,7 +5111,7 @@
         <x:v>투자 기간</x:v>
       </x:c>
       <x:c r="B13" s="5" t="str">
-        <x:v>각성 누적 55파편. 주당 21회 마탑 뽑기 기준으로 미보유 특정 스킬의 평균 개화 기간은 54회, 약 2.57주입니다. 기존 파편과 최초 보상은 제외합니다.</x:v>
+        <x:v>각성 누적 55파편. 미보유 특정 스킬은 해금 1회와 중복 2회가 필요하여 평균 48회, 주당 21회 기준 약 2.29주입니다. 기존 파편과 최초 보상은 제외합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="62" customHeight="1">
@@ -5036,7 +5119,7 @@
         <x:v>확률 편차</x:v>
       </x:c>
       <x:c r="B14" s="5" t="str">
-        <x:v>Acquisition의 P90은 정확한 음이항 계산입니다. 스킬당 95회까지 약 90%가 목표를 달성합니다. 천장이나 기간 보장은 없습니다.</x:v>
+        <x:v>미보유에서 개화까지의 P90은 음이항 계산 기준 84회입니다. 천장이나 기간 보장은 없습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="84" customHeight="1">
@@ -5044,7 +5127,7 @@
         <x:v>특수 개화</x:v>
       </x:c>
       <x:c r="B15" s="5" t="str">
-        <x:v>천벌은 약 2초 예고 후 고정 반경 2.1 월드 단위 안 최대 10체를 공격합니다. 기기 비율이 피해 범위를 바꾸지 않습니다. Bloom의 최소·최대 반경은 모두 2.1입니다. 만년빙정은 시전 시작 시 유효 적 1체 여부로 단일/다수 형태를 선택합니다.</x:v>
+        <x:v>천벌: 2초 예고, 반경 2.1, 최대 10체. 만년빙정: 적 1체면 빙정, 다수면 8개×2회, 기절 없음. 메테오: 유성우 대신 거대 운석·3.5초 균열 장판·적 60% 감속. 세 형태 모두 A10에서 전환합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="62" customHeight="1">
@@ -5060,7 +5143,7 @@
         <x:v>개화 아이콘</x:v>
       </x:c>
       <x:c r="B17" s="5" t="str">
-        <x:v>개화 ON이면 BloomIcon을 사용합니다. 기본 실루엣과 구도를 유지하고 작은 발광·색조만 변화합니다. OFF 및 미해금 상태는 원본 아이콘을 사용합니다.</x:v>
+        <x:v>기본/개화 아이콘과 이름을 전환합니다. 일반 라이트닝은 세 가닥, 천벌은 기존 구도의 보라색 뇌운/낙뢰. 메테오는 운석과 뜨거운 균열, 만년빙정은 여러 송곳과 큰 중심 빙정입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="84" customHeight="1">
@@ -5068,7 +5151,7 @@
         <x:v>타격 연출</x:v>
       </x:c>
       <x:c r="B18" s="5" t="str">
-        <x:v>타격 시점에 피해·피격 반응·효과음을 맞춥니다. 별빛은 겹쳐 낙하하고 운석은 충돌 후 잔열을 남깁니다. 기절과 감속은 독립 만료하며 감속은 합산하지 않고 가장 강한 효과만 적용합니다. 전장 전환 시 진행 중인 타격과 이펙트를 취소합니다.</x:v>
+        <x:v>낙뢰마다 약한 흔들림, 천벌·메테오 충돌 시 절제된 강한 흔들림. 화면 흔들림 설정을 따르며 연속 흔들림을 합산하지 않습니다. 지속 장판·작은 착탄 파동은 후면입니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="84" customHeight="1">
@@ -5076,7 +5159,7 @@
         <x:v>외부 원본</x:v>
       </x:c>
       <x:c r="B19" s="5" t="str">
-        <x:v>ExternalAssets 원본은 보존합니다. 제작 출처: AI/comfyui/mage-vfx/revision1~5. 일반 라이트닝은 최초 ThunderEffects 원화 복원. 운석은 Comfy 표면 마스터를 회전·화염 흐름·파편 48프레임으로 가공했습니다.</x:v>
+        <x:v>ExternalAssets 원본 보존. 아트 공정 AI/comfyui/mage-vfx/revision1~6. v6은 기존 도트를 결정론적으로 재조합하고 Comfy의 색상 행렬·16색 양자화로 아이콘을 마감했습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="62" customHeight="1">
@@ -5100,7 +5183,7 @@
         <x:v>보류 개화</x:v>
       </x:c>
       <x:c r="B22" s="5" t="str">
-        <x:v>천벌·만년빙정 외 7종은 개화 미정이며 피해 또는 회복량이 15% 증가합니다.</x:v>
+        <x:v>천벌·만년빙정·메테오 외 5종은 전용 메커니즘 미정이며 피해 또는 회복량이 15% 증가합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="68" customHeight="1">
@@ -5124,7 +5207,7 @@
         <x:v>조준 구도</x:v>
       </x:c>
       <x:c r="B25" s="24" t="str">
-        <x:v>발 위치 기준 원형 게임 판정과 쿼터뷰 타원 장판 표시를 구분합니다. 분산 스킬인 얼음 송곳·유성우는 드래그 시전과 쿨다운 소비를 하지 않습니다.</x:v>
+        <x:v>유성우 기본형과 얼음 송곳은 드래그/쿨타임 소비가 없습니다. 메테오는 지점 시전 가능. 작은 파동·메테오 장판은 보이는 타원과 동일한 발 위치 판정을 사용합니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="68" customHeight="1">
@@ -5132,7 +5215,7 @@
         <x:v>각성 안내</x:v>
       </x:c>
       <x:c r="B26" s="24" t="str">
-        <x:v>A4/A8 추가 타격·틱, 다음 각성의 효과량·쿨타임·타격 수, A10 개화 효과를 상세 화면에 표시합니다. 운석은 추가 타격 보너스가 없습니다.</x:v>
+        <x:v>A4/A8 추가 타격·틱과 다음 각성 수치를 표시합니다. 메테오에는 유성우 기본형의 추가 낙하 수를 적용하지 않습니다.</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="68" customHeight="1">
@@ -5151,10 +5234,18 @@
         <x:v>핵심 VFX 목표 32px/월드 단위, 4~6색·Point·ASTC4×4. 단발 타격은 전면, 독 늪·잔열·흡인 등 지속 장판은 후면입니다. 이펙트가 큰 경우 원본 논리 해상도도 함께 높입니다.</x:v>
       </x:c>
     </x:row>
+    <x:row r="29" ht="110" customHeight="1">
+      <x:c r="A29" t="str">
+        <x:v>운석 통합</x:v>
+      </x:c>
+      <x:c r="B29" t="str">
+        <x:v>높은 E/A를 보존. 낮은 E의 실제 비전 지식 지출을 전액 환급, 낮은 A에 쓴 파편과 남은 파편을 합산. 둘 다 보유했으면 중복 보유 30파편 추가. 기존 내역을 보관하고 한 번만 적용. 기존 운석 슬롯은 유성우가 없을 때 교체하며, 이미 장착했다면 해당 슬롯만 비웁니다.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re36db18132344b88"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaf48e4e26674f91"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/Assets/_Project/Scripts/Skill_Catalog.xlsx
+++ b/Assets/_Project/Scripts/Skill_Catalog.xlsx
@@ -2,14 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R2b25563ab4234517"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R252594dbfc684dd0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R9949f6ace02f4682"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="R55d581f3c3644ed7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R0397ae5074cf4a68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="Rdcad8e5da80041fd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="Rf4e5a5af546e4974"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="Rbdb279aa60c54caf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Skills" sheetId="1" r:id="R49790a27f37d4edd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Parameters" sheetId="2" r:id="R7bc3355c6b47471a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bloom" sheetId="3" r:id="R7859613883c44701"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acquisition" sheetId="4" r:id="Rde563dac25514508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Growth" sheetId="5" r:id="R7e9539031e0b41eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assets" sheetId="6" r:id="R1270c1c6fcee4214"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Targeting" sheetId="7" r:id="R1c48d1746ece4496"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="8" r:id="Ra724209d916a4c30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -26,7 +26,7 @@
     <x:numFmt numFmtId="202" formatCode="0.00"/>
     <x:numFmt numFmtId="203" formatCode="0.0000"/>
   </x:numFmts>
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -69,8 +69,13 @@
       <x:color rgb="FF6B7280"/>
       <x:name val="Malgun Gothic"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF6B7280"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -87,6 +92,11 @@
         <x:fgColor rgb="FFE5E7EB"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFE5E7EB"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="1">
     <x:border/>
@@ -94,7 +104,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="46">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -240,6 +250,31 @@
     <x:xf numFmtId="202" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+      <x:extLst>
+        <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" i="0"/>
+        </x:ext>
+      </x:extLst>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -361,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="Mage_Assets" displayName="Mage_Assets" ref="A1:J10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:tableColumns count="10">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="Mage_Assets" displayName="Mage_Assets" ref="A1:K10" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:tableColumns count="11">
     <x:tableColumn id="1" name="SkillId"/>
     <x:tableColumn id="2" name="Key"/>
     <x:tableColumn id="3" name="SkillAssetPath"/>
@@ -373,6 +408,7 @@
     <x:tableColumn id="8" name="SecondaryPrefabPath"/>
     <x:tableColumn id="9" name="BloomPrefabPath"/>
     <x:tableColumn id="10" name="BloomCastingPrefabPath"/>
+    <x:tableColumn id="11" name="BloomSecondaryPrefabPath"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -391,7 +427,7 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Mage_Guide" displayName="Mage_Guide" ref="A1:B22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="Mage_Guide" displayName="Mage_Guide" ref="A1:B29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="Topic"/>
     <x:tableColumn id="2" name="Description"/>
@@ -842,31 +878,31 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="70" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str">
+      <x:c r="C9" s="39" t="str">
         <x:v>독립 운석 삭제</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="D9" s="39" t="str">
         <x:v>ID 3 개화로 통합</x:v>
       </x:c>
-      <x:c r="E9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="28" t="str">
+      <x:c r="E9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="39" t="str">
         <x:v>ID 8은 비활성 보존 ID입니다. 로스터·장착·뽑기에 나오지 않으며 유성우의 개화 메테오로 통합했습니다.</x:v>
       </x:c>
     </x:row>
@@ -913,7 +949,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36a81b40f5f3428a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R361e8e086d3249e9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1314,50 +1350,50 @@
       <x:c r="O8" s="5"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:f>'Skills'!B9</x:f>
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="32" t="n">
+      <x:c r="C9" s="40" t="n">
         <x:v>1.5499999523162842</x:v>
       </x:c>
-      <x:c r="D9" s="32" t="n">
+      <x:c r="D9" s="40" t="n">
         <x:v>0.800000011920929</x:v>
       </x:c>
-      <x:c r="E9" s="32" t="n">
+      <x:c r="E9" s="40" t="n">
         <x:v>0.800000011920929</x:v>
       </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
+      <x:c r="F9" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="40" t="n">
         <x:v>0.13461539149284363</x:v>
       </x:c>
-      <x:c r="I9" s="33" t="b">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="28" t="str">
+      <x:c r="I9" s="41" t="b">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="39" t="str">
         <x:v>충돌 1회 + 잔열 2회</x:v>
       </x:c>
-      <x:c r="K9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="L9" s="27" t="n">
+      <x:c r="K9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9" s="38" t="n">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="M9" s="27" t="n">
+      <x:c r="M9" s="38" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="N9" s="28" t="str">
+      <x:c r="N9" s="39" t="str">
         <x:v>Fire_Tornado_SFX</x:v>
       </x:c>
-      <x:c r="O9" s="28"/>
+      <x:c r="O9" s="39"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -1425,7 +1461,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a404bc63e948f8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9709b4067f404c24"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1752,37 +1788,37 @@
       <x:c r="N8" s="5"/>
     </x:row>
     <x:row r="9" ht="90" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:f>'Skills'!C9</x:f>
         <x:v>독립 운석 삭제</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str">
+      <x:c r="C9" s="39" t="str">
         <x:v>통합됨</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="D9" s="39" t="str">
         <x:v>ID 3 메테오 개화 항목을 사용합니다.</x:v>
       </x:c>
-      <x:c r="E9" s="27" t="n">
+      <x:c r="E9" s="38" t="n">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="F9" s="27" t="n">
+      <x:c r="F9" s="38" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="G9" s="27" t="n">
+      <x:c r="G9" s="38" t="n">
         <x:v>1.149999976158142</x:v>
       </x:c>
-      <x:c r="H9" s="28"/>
-      <x:c r="I9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="28"/>
-      <x:c r="K9" s="28"/>
-      <x:c r="L9" s="28"/>
-      <x:c r="M9" s="28"/>
-      <x:c r="N9" s="28"/>
+      <x:c r="H9" s="39"/>
+      <x:c r="I9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="39"/>
+      <x:c r="K9" s="39"/>
+      <x:c r="L9" s="39"/>
+      <x:c r="M9" s="39"/>
+      <x:c r="N9" s="39"/>
     </x:row>
     <x:row r="10" ht="90" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -1836,7 +1872,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R49f09b68380e4338"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf3cee35716e045c2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2152,35 +2188,35 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:f>'Skills'!C9</x:f>
         <x:v>독립 운석 삭제</x:v>
       </x:c>
-      <x:c r="C9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="36" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="27" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="28" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H9" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I9" s="37" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="J9" s="27" t="n">
+      <x:c r="C9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I9" s="43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J9" s="38" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -2236,7 +2272,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5e7c2d7649541c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R23e47c6a2d6341fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4492,7 +4528,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82e861d794534565"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R00f3df0dc3444bdb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4753,32 +4789,32 @@
       <x:c r="K8" t="str"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:f>'Skills'!B9</x:f>
         <x:v>Meteor</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str">
+      <x:c r="C9" s="39" t="str">
         <x:v>Assets/MageTower/SO/Meteor/MageTowerSkill_Meteor.asset</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="D9" s="39" t="str">
         <x:v>Assets/_Project/Art/Icons/MageTower/Meteor.png</x:v>
       </x:c>
-      <x:c r="E9" s="28" t="str">
+      <x:c r="E9" s="39" t="str">
         <x:v>Assets/_Project/Art/Icons/MageTower/Meteor_Bloom.png</x:v>
       </x:c>
-      <x:c r="F9" s="28" t="str">
+      <x:c r="F9" s="39" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/Meteor.prefab</x:v>
       </x:c>
-      <x:c r="G9" s="28" t="str"/>
-      <x:c r="H9" s="28" t="str">
+      <x:c r="G9" s="39" t="str"/>
+      <x:c r="H9" s="39" t="str">
         <x:v>Assets/_Project/Prefabs/VFX/MageTower/MeteorCrater.prefab</x:v>
       </x:c>
-      <x:c r="I9" s="28"/>
-      <x:c r="J9" s="28"/>
-      <x:c r="K9" t="str"/>
+      <x:c r="I9" s="39"/>
+      <x:c r="J9" s="39"/>
+      <x:c r="K9" s="45" t="str"/>
     </x:row>
     <x:row r="10" ht="34" customHeight="1">
       <x:c r="A10" s="9" t="n">
@@ -4823,7 +4859,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ec304716b734fa4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5faedbaba3e3420a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4958,16 +4994,16 @@
       </x:c>
     </x:row>
     <x:row r="9" ht="76" customHeight="1">
-      <x:c r="A9" s="27" t="n">
+      <x:c r="A9" s="38" t="n">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B9" s="28" t="str">
+      <x:c r="B9" s="39" t="str">
         <x:v>비활성 보존 ID</x:v>
       </x:c>
-      <x:c r="C9" s="28" t="str">
+      <x:c r="C9" s="39" t="str">
         <x:v>ID 3 기본 유성우 / 개화 메테오를 참조.</x:v>
       </x:c>
-      <x:c r="D9" s="28" t="str">
+      <x:c r="D9" s="39" t="str">
         <x:v>운석과 폭발 전면 · 잔열 후면</x:v>
       </x:c>
     </x:row>
@@ -4994,7 +5030,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4399e50245884bf9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7f97ac94de5f41ee"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5245,7 +5281,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcaf48e4e26674f91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rde8ed5ee0e8e465f"/>
   </x:tableParts>
 </x:worksheet>
 </file>